--- a/research/traditional_assets/database/data/spain/spain_air_transport.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_air_transport.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09778676894003105</v>
+        <v>0.09757605201768098</v>
       </c>
       <c r="C2">
-        <v>38423.21523355559</v>
+        <v>38146.3558500933</v>
       </c>
       <c r="D2">
-        <v>35986.11523355559</v>
+        <v>36103.7978500933</v>
       </c>
       <c r="E2">
-        <v>-8798.799999999999</v>
+        <v>-8404.258</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>394.542</v>
       </c>
       <c r="G2">
         <v>2437.1</v>
@@ -1457,28 +1457,28 @@
         <v>2746.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>19.8454626</v>
       </c>
       <c r="N2">
-        <v>2746.3</v>
+        <v>2726.4545374</v>
       </c>
       <c r="O2">
-        <v>686.575</v>
+        <v>681.6136343500001</v>
       </c>
       <c r="P2">
-        <v>2059.725</v>
+        <v>2044.84090305</v>
       </c>
       <c r="Q2">
-        <v>3010.025000000001</v>
+        <v>2995.14090305</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09778676894003105</v>
+        <v>0.09818060809866766</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8103113482567638</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.3842773209026</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09757605201768098</v>
+        <v>0.09736533509533089</v>
       </c>
       <c r="C3">
-        <v>38146.3558500933</v>
+        <v>37870.26868873412</v>
       </c>
       <c r="D3">
-        <v>36103.7978500933</v>
+        <v>36222.25268873412</v>
       </c>
       <c r="E3">
-        <v>-8404.258</v>
+        <v>-8009.715999999999</v>
       </c>
       <c r="F3">
-        <v>394.542</v>
+        <v>789.0839999999999</v>
       </c>
       <c r="G3">
         <v>2437.1</v>
@@ -1539,28 +1539,28 @@
         <v>2746.3</v>
       </c>
       <c r="M3">
-        <v>19.8454626</v>
+        <v>39.6909252</v>
       </c>
       <c r="N3">
-        <v>2726.4545374</v>
+        <v>2706.6090748</v>
       </c>
       <c r="O3">
-        <v>681.6136343500001</v>
+        <v>676.6522687</v>
       </c>
       <c r="P3">
-        <v>2044.84090305</v>
+        <v>2029.9568061</v>
       </c>
       <c r="Q3">
-        <v>2995.14090305</v>
+        <v>2980.2568061</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09818060809866766</v>
+        <v>0.09858248479115397</v>
       </c>
       <c r="T3">
-        <v>0.8103113482567638</v>
+        <v>0.8165282528774234</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.3842773209026</v>
+        <v>69.19213866045129</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09736533509533089</v>
+        <v>0.09715461817298081</v>
       </c>
       <c r="C4">
-        <v>37870.26868873412</v>
+        <v>37594.96137536988</v>
       </c>
       <c r="D4">
-        <v>36222.25268873412</v>
+        <v>36341.48737536988</v>
       </c>
       <c r="E4">
-        <v>-8009.715999999999</v>
+        <v>-7615.173999999999</v>
       </c>
       <c r="F4">
-        <v>789.0839999999999</v>
+        <v>1183.626</v>
       </c>
       <c r="G4">
         <v>2437.1</v>
@@ -1621,28 +1621,28 @@
         <v>2746.3</v>
       </c>
       <c r="M4">
-        <v>39.6909252</v>
+        <v>59.53638779999999</v>
       </c>
       <c r="N4">
-        <v>2706.6090748</v>
+        <v>2686.7636122</v>
       </c>
       <c r="O4">
-        <v>676.6522687</v>
+        <v>671.6909030500001</v>
       </c>
       <c r="P4">
-        <v>2029.9568061</v>
+        <v>2015.07270915</v>
       </c>
       <c r="Q4">
-        <v>2980.2568061</v>
+        <v>2965.37270915</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09858248479115397</v>
+        <v>0.09899264760101115</v>
       </c>
       <c r="T4">
-        <v>0.8165282528774234</v>
+        <v>0.8228733410985087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.19213866045129</v>
+        <v>46.12809244030087</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09715461817298081</v>
+        <v>0.09694390125063074</v>
       </c>
       <c r="C5">
-        <v>37594.96137536988</v>
+        <v>37320.44163663423</v>
       </c>
       <c r="D5">
-        <v>36341.48737536988</v>
+        <v>36461.50963663423</v>
       </c>
       <c r="E5">
-        <v>-7615.173999999999</v>
+        <v>-7220.632</v>
       </c>
       <c r="F5">
-        <v>1183.626</v>
+        <v>1578.168</v>
       </c>
       <c r="G5">
         <v>2437.1</v>
@@ -1703,28 +1703,28 @@
         <v>2746.3</v>
       </c>
       <c r="M5">
-        <v>59.53638779999999</v>
+        <v>79.38185039999999</v>
       </c>
       <c r="N5">
-        <v>2686.7636122</v>
+        <v>2666.9181496</v>
       </c>
       <c r="O5">
-        <v>671.6909030500001</v>
+        <v>666.7295374</v>
       </c>
       <c r="P5">
-        <v>2015.07270915</v>
+        <v>2000.1886122</v>
       </c>
       <c r="Q5">
-        <v>2965.37270915</v>
+        <v>2950.4886122</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09899264760101115</v>
+        <v>0.09941135546940702</v>
       </c>
       <c r="T5">
-        <v>0.8228733410985087</v>
+        <v>0.8293506186575337</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.12809244030087</v>
+        <v>34.59606933022565</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09694390125063074</v>
+        <v>0.09673318432828067</v>
       </c>
       <c r="C6">
-        <v>37320.44163663423</v>
+        <v>37046.71730157171</v>
       </c>
       <c r="D6">
-        <v>36461.50963663423</v>
+        <v>36582.32730157171</v>
       </c>
       <c r="E6">
-        <v>-7220.632</v>
+        <v>-6826.089999999999</v>
       </c>
       <c r="F6">
-        <v>1578.168</v>
+        <v>1972.71</v>
       </c>
       <c r="G6">
         <v>2437.1</v>
@@ -1785,28 +1785,28 @@
         <v>2746.3</v>
       </c>
       <c r="M6">
-        <v>79.38185039999999</v>
+        <v>99.227313</v>
       </c>
       <c r="N6">
-        <v>2666.9181496</v>
+        <v>2647.072687</v>
       </c>
       <c r="O6">
-        <v>666.7295374</v>
+        <v>661.7681717500001</v>
       </c>
       <c r="P6">
-        <v>2000.1886122</v>
+        <v>1985.30451525</v>
       </c>
       <c r="Q6">
-        <v>2950.4886122</v>
+        <v>2935.60451525</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09941135546940702</v>
+        <v>0.09983887824029544</v>
       </c>
       <c r="T6">
-        <v>0.8293506186575337</v>
+        <v>0.8359642599546432</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.59606933022565</v>
+        <v>27.67685546418052</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09673318432828067</v>
+        <v>0.09652246740593058</v>
       </c>
       <c r="C7">
-        <v>37046.71730157171</v>
+        <v>36773.79630334011</v>
       </c>
       <c r="D7">
-        <v>36582.32730157171</v>
+        <v>36703.94830334011</v>
       </c>
       <c r="E7">
-        <v>-6826.089999999999</v>
+        <v>-6431.547999999999</v>
       </c>
       <c r="F7">
-        <v>1972.71</v>
+        <v>2367.252</v>
       </c>
       <c r="G7">
         <v>2437.1</v>
@@ -1867,28 +1867,28 @@
         <v>2746.3</v>
       </c>
       <c r="M7">
-        <v>99.227313</v>
+        <v>119.0727756</v>
       </c>
       <c r="N7">
-        <v>2647.072687</v>
+        <v>2627.2272244</v>
       </c>
       <c r="O7">
-        <v>661.7681717500001</v>
+        <v>656.8068061</v>
       </c>
       <c r="P7">
-        <v>1985.30451525</v>
+        <v>1970.4204183</v>
       </c>
       <c r="Q7">
-        <v>2935.60451525</v>
+        <v>2920.7204183</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09983887824029544</v>
+        <v>0.1002754972403517</v>
       </c>
       <c r="T7">
-        <v>0.8359642599546432</v>
+        <v>0.8427186170240316</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.67685546418052</v>
+        <v>23.06404622015043</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09652246740593058</v>
+        <v>0.0963117504835805</v>
       </c>
       <c r="C8">
-        <v>36773.79630334011</v>
+        <v>36501.68668094691</v>
       </c>
       <c r="D8">
-        <v>36703.94830334011</v>
+        <v>36826.38068094692</v>
       </c>
       <c r="E8">
-        <v>-6431.547999999999</v>
+        <v>-6037.005999999999</v>
       </c>
       <c r="F8">
-        <v>2367.252</v>
+        <v>2761.793999999999</v>
       </c>
       <c r="G8">
         <v>2437.1</v>
@@ -1949,28 +1949,28 @@
         <v>2746.3</v>
       </c>
       <c r="M8">
-        <v>119.0727756</v>
+        <v>138.9182382</v>
       </c>
       <c r="N8">
-        <v>2627.2272244</v>
+        <v>2607.3817618</v>
       </c>
       <c r="O8">
-        <v>656.8068061</v>
+        <v>651.8454404500001</v>
       </c>
       <c r="P8">
-        <v>1970.4204183</v>
+        <v>1955.53632135</v>
       </c>
       <c r="Q8">
-        <v>2920.7204183</v>
+        <v>2905.83632135</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1002754972403517</v>
+        <v>0.1007215058963231</v>
       </c>
       <c r="T8">
-        <v>0.8427186170240316</v>
+        <v>0.8496182290841595</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.06404622015043</v>
+        <v>19.76918247441466</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09631175048358048</v>
+        <v>0.09610103356123043</v>
       </c>
       <c r="C9">
-        <v>36501.68668094692</v>
+        <v>36230.39658102056</v>
       </c>
       <c r="D9">
-        <v>36826.38068094692</v>
+        <v>36949.63258102057</v>
       </c>
       <c r="E9">
-        <v>-6037.005999999999</v>
+        <v>-5642.464</v>
       </c>
       <c r="F9">
-        <v>2761.794</v>
+        <v>3156.336</v>
       </c>
       <c r="G9">
         <v>2437.1</v>
@@ -2031,28 +2031,28 @@
         <v>2746.3</v>
       </c>
       <c r="M9">
-        <v>138.9182382</v>
+        <v>158.7637008</v>
       </c>
       <c r="N9">
-        <v>2607.3817618</v>
+        <v>2587.5362992</v>
       </c>
       <c r="O9">
-        <v>651.8454404500001</v>
+        <v>646.8840748</v>
       </c>
       <c r="P9">
-        <v>1955.53632135</v>
+        <v>1940.6522244</v>
       </c>
       <c r="Q9">
-        <v>2905.83632135</v>
+        <v>2890.9522244</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1007215058963231</v>
+        <v>0.1011772103926418</v>
       </c>
       <c r="T9">
-        <v>0.8496182290841595</v>
+        <v>0.8566678327108121</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.76918247441466</v>
+        <v>17.29803466511282</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09610103356123043</v>
+        <v>0.09589031663888035</v>
       </c>
       <c r="C10">
-        <v>36230.39658102056</v>
+        <v>35959.93425961753</v>
       </c>
       <c r="D10">
-        <v>36949.63258102057</v>
+        <v>37073.71225961753</v>
       </c>
       <c r="E10">
-        <v>-5642.464</v>
+        <v>-5247.922</v>
       </c>
       <c r="F10">
-        <v>3156.336</v>
+        <v>3550.878</v>
       </c>
       <c r="G10">
         <v>2437.1</v>
@@ -2113,28 +2113,28 @@
         <v>2746.3</v>
       </c>
       <c r="M10">
-        <v>158.7637008</v>
+        <v>178.6091634</v>
       </c>
       <c r="N10">
-        <v>2587.5362992</v>
+        <v>2567.6908366</v>
       </c>
       <c r="O10">
-        <v>646.8840748</v>
+        <v>641.9227091500001</v>
       </c>
       <c r="P10">
-        <v>1940.6522244</v>
+        <v>1925.76812745</v>
       </c>
       <c r="Q10">
-        <v>2890.9522244</v>
+        <v>2876.06812745</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1011772103926418</v>
+        <v>0.101642930372396</v>
       </c>
       <c r="T10">
-        <v>0.8566678327108121</v>
+        <v>0.8638723726809074</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.29803466511282</v>
+        <v>15.37603081343362</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09589031663888035</v>
+        <v>0.09567959971653028</v>
       </c>
       <c r="C11">
-        <v>35959.93425961753</v>
+        <v>35690.30808406581</v>
       </c>
       <c r="D11">
-        <v>37073.71225961753</v>
+        <v>37198.62808406581</v>
       </c>
       <c r="E11">
-        <v>-5247.922</v>
+        <v>-4853.38</v>
       </c>
       <c r="F11">
-        <v>3550.878</v>
+        <v>3945.419999999999</v>
       </c>
       <c r="G11">
         <v>2437.1</v>
@@ -2195,28 +2195,28 @@
         <v>2746.3</v>
       </c>
       <c r="M11">
-        <v>178.6091634</v>
+        <v>198.454626</v>
       </c>
       <c r="N11">
-        <v>2567.6908366</v>
+        <v>2547.845374</v>
       </c>
       <c r="O11">
-        <v>641.9227091500001</v>
+        <v>636.9613435000001</v>
       </c>
       <c r="P11">
-        <v>1925.76812745</v>
+        <v>1910.8840305</v>
       </c>
       <c r="Q11">
-        <v>2876.06812745</v>
+        <v>2861.184030500001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.101642930372396</v>
+        <v>0.1021189996850336</v>
       </c>
       <c r="T11">
-        <v>0.8638723726809074</v>
+        <v>0.8712370135392272</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.37603081343362</v>
+        <v>13.83842773209026</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09567959971653028</v>
+        <v>0.0954688827941802</v>
       </c>
       <c r="C12">
-        <v>35690.30808406581</v>
+        <v>35421.52653484584</v>
       </c>
       <c r="D12">
-        <v>37198.62808406581</v>
+        <v>37324.38853484584</v>
       </c>
       <c r="E12">
-        <v>-4853.379999999999</v>
+        <v>-4458.838</v>
       </c>
       <c r="F12">
-        <v>3945.42</v>
+        <v>4339.962</v>
       </c>
       <c r="G12">
         <v>2437.1</v>
@@ -2277,28 +2277,28 @@
         <v>2746.3</v>
       </c>
       <c r="M12">
-        <v>198.454626</v>
+        <v>218.3000886</v>
       </c>
       <c r="N12">
-        <v>2547.845374</v>
+        <v>2527.9999114</v>
       </c>
       <c r="O12">
-        <v>636.9613435</v>
+        <v>631.9999778500001</v>
       </c>
       <c r="P12">
-        <v>1910.8840305</v>
+        <v>1895.99993355</v>
       </c>
       <c r="Q12">
-        <v>2861.1840305</v>
+        <v>2846.29993355</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1021189996850336</v>
+        <v>0.1026057671844721</v>
       </c>
       <c r="T12">
-        <v>0.8712370135392272</v>
+        <v>0.8787671519449251</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.83842773209026</v>
+        <v>12.58038884735478</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0954688827941802</v>
+        <v>0.09525816587183011</v>
       </c>
       <c r="C13">
-        <v>35421.52653484584</v>
+        <v>35153.59820750968</v>
       </c>
       <c r="D13">
-        <v>37324.38853484584</v>
+        <v>37451.00220750969</v>
       </c>
       <c r="E13">
-        <v>-4458.838</v>
+        <v>-4064.295999999999</v>
       </c>
       <c r="F13">
-        <v>4339.962</v>
+        <v>4734.504</v>
       </c>
       <c r="G13">
         <v>2437.1</v>
@@ -2359,28 +2359,28 @@
         <v>2746.3</v>
       </c>
       <c r="M13">
-        <v>218.3000886</v>
+        <v>238.1455512</v>
       </c>
       <c r="N13">
-        <v>2527.9999114</v>
+        <v>2508.1544488</v>
       </c>
       <c r="O13">
-        <v>631.9999778500001</v>
+        <v>627.0386122000001</v>
       </c>
       <c r="P13">
-        <v>1895.99993355</v>
+        <v>1881.1158366</v>
       </c>
       <c r="Q13">
-        <v>2846.29993355</v>
+        <v>2831.4158366</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1026057671844721</v>
+        <v>0.1031035975816251</v>
       </c>
       <c r="T13">
-        <v>0.8787671519449251</v>
+        <v>0.8864684298598431</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.58038884735478</v>
+        <v>11.53202311007522</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09525816587183011</v>
+        <v>0.09504744894948004</v>
       </c>
       <c r="C14">
-        <v>35153.59820750968</v>
+        <v>34886.53181463949</v>
       </c>
       <c r="D14">
-        <v>37451.00220750969</v>
+        <v>37578.47781463949</v>
       </c>
       <c r="E14">
-        <v>-4064.295999999999</v>
+        <v>-3669.754</v>
       </c>
       <c r="F14">
-        <v>4734.504</v>
+        <v>5129.045999999999</v>
       </c>
       <c r="G14">
         <v>2437.1</v>
@@ -2441,28 +2441,28 @@
         <v>2746.3</v>
       </c>
       <c r="M14">
-        <v>238.1455512</v>
+        <v>257.9910138</v>
       </c>
       <c r="N14">
-        <v>2508.1544488</v>
+        <v>2488.3089862</v>
       </c>
       <c r="O14">
-        <v>627.0386122000001</v>
+        <v>622.07724655</v>
       </c>
       <c r="P14">
-        <v>1881.1158366</v>
+        <v>1866.23173965</v>
       </c>
       <c r="Q14">
-        <v>2831.4158366</v>
+        <v>2816.53173965</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1031035975816251</v>
+        <v>0.1036128723557242</v>
       </c>
       <c r="T14">
-        <v>0.8864684298598431</v>
+        <v>0.8943467486463685</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.53202311007522</v>
+        <v>10.6449444093002</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09504744894948004</v>
+        <v>0.09483673202712996</v>
       </c>
       <c r="C15">
-        <v>34886.53181463949</v>
+        <v>34620.336187846</v>
       </c>
       <c r="D15">
-        <v>37578.47781463949</v>
+        <v>37706.824187846</v>
       </c>
       <c r="E15">
-        <v>-3669.754</v>
+        <v>-3275.212</v>
       </c>
       <c r="F15">
-        <v>5129.045999999999</v>
+        <v>5523.588</v>
       </c>
       <c r="G15">
         <v>2437.1</v>
@@ -2523,28 +2523,28 @@
         <v>2746.3</v>
       </c>
       <c r="M15">
-        <v>257.9910138</v>
+        <v>277.8364764</v>
       </c>
       <c r="N15">
-        <v>2488.3089862</v>
+        <v>2468.4635236</v>
       </c>
       <c r="O15">
-        <v>622.07724655</v>
+        <v>617.1158809000001</v>
       </c>
       <c r="P15">
-        <v>1866.23173965</v>
+        <v>1851.3476427</v>
       </c>
       <c r="Q15">
-        <v>2816.53173965</v>
+        <v>2801.6476427</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1036128723557242</v>
+        <v>0.1041339907292209</v>
       </c>
       <c r="T15">
-        <v>0.8943467486463685</v>
+        <v>0.9024082841488597</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.6449444093002</v>
+        <v>9.884591237207328</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09483673202712996</v>
+        <v>0.09462601510477989</v>
       </c>
       <c r="C16">
-        <v>34620.336187846</v>
+        <v>34355.02027980814</v>
       </c>
       <c r="D16">
-        <v>37706.824187846</v>
+        <v>37836.05027980814</v>
       </c>
       <c r="E16">
-        <v>-3275.212</v>
+        <v>-2880.669999999999</v>
       </c>
       <c r="F16">
-        <v>5523.588</v>
+        <v>5918.13</v>
       </c>
       <c r="G16">
         <v>2437.1</v>
@@ -2605,28 +2605,28 @@
         <v>2746.3</v>
       </c>
       <c r="M16">
-        <v>277.8364764</v>
+        <v>297.681939</v>
       </c>
       <c r="N16">
-        <v>2468.4635236</v>
+        <v>2448.618061</v>
       </c>
       <c r="O16">
-        <v>617.1158809000001</v>
+        <v>612.15451525</v>
       </c>
       <c r="P16">
-        <v>1851.3476427</v>
+        <v>1836.46354575</v>
       </c>
       <c r="Q16">
-        <v>2801.6476427</v>
+        <v>2786.76354575</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1041339907292209</v>
+        <v>0.1046673707115058</v>
       </c>
       <c r="T16">
-        <v>0.9024082841488597</v>
+        <v>0.9106595028396448</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.884591237207328</v>
+        <v>9.225618488060171</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09462601510477989</v>
+        <v>0.0945952981824298</v>
       </c>
       <c r="C17">
-        <v>34355.02027980814</v>
+        <v>33979.39001397998</v>
       </c>
       <c r="D17">
-        <v>37836.05027980814</v>
+        <v>37854.96201397998</v>
       </c>
       <c r="E17">
-        <v>-2880.67</v>
+        <v>-2486.128</v>
       </c>
       <c r="F17">
-        <v>5918.129999999999</v>
+        <v>6312.672</v>
       </c>
       <c r="G17">
         <v>2437.1</v>
@@ -2687,45 +2687,45 @@
         <v>2746.3</v>
       </c>
       <c r="M17">
-        <v>297.6819389999999</v>
+        <v>326.9964096</v>
       </c>
       <c r="N17">
-        <v>2448.618061</v>
+        <v>2419.3035904</v>
       </c>
       <c r="O17">
-        <v>612.15451525</v>
+        <v>604.8258976000001</v>
       </c>
       <c r="P17">
-        <v>1836.46354575</v>
+        <v>1814.4776928</v>
       </c>
       <c r="Q17">
-        <v>2786.76354575</v>
+        <v>2764.7776928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1046673707115058</v>
+        <v>0.1052134502171783</v>
       </c>
       <c r="T17">
-        <v>0.9106595028396448</v>
+        <v>0.9191071791183056</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.225618488060173</v>
+        <v>8.398563162694739</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0945952981824298</v>
+        <v>0.09439583126007974</v>
       </c>
       <c r="C18">
-        <v>33979.39001397998</v>
+        <v>33708.11690200592</v>
       </c>
       <c r="D18">
-        <v>37854.96201397998</v>
+        <v>37978.23090200593</v>
       </c>
       <c r="E18">
-        <v>-2486.128</v>
+        <v>-2091.585999999999</v>
       </c>
       <c r="F18">
-        <v>6312.672</v>
+        <v>6707.214</v>
       </c>
       <c r="G18">
         <v>2437.1</v>
@@ -2769,28 +2769,28 @@
         <v>2746.3</v>
       </c>
       <c r="M18">
-        <v>326.9964096</v>
+        <v>347.4336852</v>
       </c>
       <c r="N18">
-        <v>2419.3035904</v>
+        <v>2398.8663148</v>
       </c>
       <c r="O18">
-        <v>604.8258976000001</v>
+        <v>599.7165787</v>
       </c>
       <c r="P18">
-        <v>1814.4776928</v>
+        <v>1799.1497361</v>
       </c>
       <c r="Q18">
-        <v>2764.7776928</v>
+        <v>2749.4497361</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1052134502171783</v>
+        <v>0.1057726882651563</v>
       </c>
       <c r="T18">
-        <v>0.9191071791183056</v>
+        <v>0.9277584138615127</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.398563162694739</v>
+        <v>7.9045300354774</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09439583126007974</v>
+        <v>0.09419636433772964</v>
       </c>
       <c r="C19">
-        <v>33708.11690200592</v>
+        <v>33437.64922533024</v>
       </c>
       <c r="D19">
-        <v>37978.23090200593</v>
+        <v>38102.30522533024</v>
       </c>
       <c r="E19">
-        <v>-2091.585999999999</v>
+        <v>-1697.043999999999</v>
       </c>
       <c r="F19">
-        <v>6707.214</v>
+        <v>7101.756</v>
       </c>
       <c r="G19">
         <v>2437.1</v>
@@ -2851,28 +2851,28 @@
         <v>2746.3</v>
       </c>
       <c r="M19">
-        <v>347.4336852</v>
+        <v>367.8709608</v>
       </c>
       <c r="N19">
-        <v>2398.8663148</v>
+        <v>2378.4290392</v>
       </c>
       <c r="O19">
-        <v>599.7165787</v>
+        <v>594.6072598000001</v>
       </c>
       <c r="P19">
-        <v>1799.1497361</v>
+        <v>1783.8217794</v>
       </c>
       <c r="Q19">
-        <v>2749.4497361</v>
+        <v>2734.1217794</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1057726882651563</v>
+        <v>0.106345566265524</v>
       </c>
       <c r="T19">
-        <v>0.9277584138615127</v>
+        <v>0.9366206543301636</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.9045300354774</v>
+        <v>7.465389477950878</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09419636433772965</v>
+        <v>0.09399689741537959</v>
       </c>
       <c r="C20">
-        <v>33437.64922533023</v>
+        <v>33167.99490386304</v>
       </c>
       <c r="D20">
-        <v>38102.30522533023</v>
+        <v>38227.19290386304</v>
       </c>
       <c r="E20">
-        <v>-1697.044</v>
+        <v>-1302.501999999999</v>
       </c>
       <c r="F20">
-        <v>7101.755999999999</v>
+        <v>7496.298</v>
       </c>
       <c r="G20">
         <v>2437.1</v>
@@ -2933,28 +2933,28 @@
         <v>2746.3</v>
       </c>
       <c r="M20">
-        <v>367.8709608</v>
+        <v>388.3082364</v>
       </c>
       <c r="N20">
-        <v>2378.4290392</v>
+        <v>2357.9917636</v>
       </c>
       <c r="O20">
-        <v>594.6072598000001</v>
+        <v>589.4979409</v>
       </c>
       <c r="P20">
-        <v>1783.8217794</v>
+        <v>1768.4938227</v>
       </c>
       <c r="Q20">
-        <v>2734.1217794</v>
+        <v>2718.7938227</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.106345566265524</v>
+        <v>0.1069325894017032</v>
       </c>
       <c r="T20">
-        <v>0.9366206543301636</v>
+        <v>0.9457017155511271</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.465389477950879</v>
+        <v>7.072474242269253</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09399689741537959</v>
+        <v>0.09379743049302951</v>
       </c>
       <c r="C21">
-        <v>33167.99490386304</v>
+        <v>32899.16196169212</v>
       </c>
       <c r="D21">
-        <v>38227.19290386304</v>
+        <v>38352.90196169212</v>
       </c>
       <c r="E21">
-        <v>-1302.501999999999</v>
+        <v>-907.9599999999991</v>
       </c>
       <c r="F21">
-        <v>7496.298</v>
+        <v>7890.84</v>
       </c>
       <c r="G21">
         <v>2437.1</v>
@@ -3015,28 +3015,28 @@
         <v>2746.3</v>
       </c>
       <c r="M21">
-        <v>388.3082364</v>
+        <v>408.745512</v>
       </c>
       <c r="N21">
-        <v>2357.9917636</v>
+        <v>2337.554488</v>
       </c>
       <c r="O21">
-        <v>589.4979409</v>
+        <v>584.3886220000001</v>
       </c>
       <c r="P21">
-        <v>1768.4938227</v>
+        <v>1753.165866</v>
       </c>
       <c r="Q21">
-        <v>2718.7938227</v>
+        <v>2703.465866</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1069325894017032</v>
+        <v>0.1075342881162869</v>
       </c>
       <c r="T21">
-        <v>0.9457017155511271</v>
+        <v>0.9550098033026145</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.072474242269253</v>
+        <v>6.718850530155791</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09379743049302951</v>
+        <v>0.09386571357067942</v>
       </c>
       <c r="C22">
-        <v>32899.16196169212</v>
+        <v>32461.49328744508</v>
       </c>
       <c r="D22">
-        <v>38352.90196169212</v>
+        <v>38309.77528744508</v>
       </c>
       <c r="E22">
-        <v>-907.9599999999991</v>
+        <v>-513.4179999999997</v>
       </c>
       <c r="F22">
-        <v>7890.84</v>
+        <v>8285.382</v>
       </c>
       <c r="G22">
         <v>2437.1</v>
@@ -3097,45 +3097,45 @@
         <v>2746.3</v>
       </c>
       <c r="M22">
-        <v>408.745512</v>
+        <v>443.267937</v>
       </c>
       <c r="N22">
-        <v>2337.554488</v>
+        <v>2303.032063</v>
       </c>
       <c r="O22">
-        <v>584.3886220000001</v>
+        <v>575.75801575</v>
       </c>
       <c r="P22">
-        <v>1753.165866</v>
+        <v>1727.27404725</v>
       </c>
       <c r="Q22">
-        <v>2703.465866</v>
+        <v>2677.57404725</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1075342881162869</v>
+        <v>0.1081512197097208</v>
       </c>
       <c r="T22">
-        <v>0.9550098033026145</v>
+        <v>0.9645535388452788</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.718850530155791</v>
+        <v>6.195575566748019</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09386571357067942</v>
+        <v>0.09367899664832935</v>
       </c>
       <c r="C23">
-        <v>32461.49328744508</v>
+        <v>32185.10989544048</v>
       </c>
       <c r="D23">
-        <v>38309.77528744508</v>
+        <v>38427.93389544048</v>
       </c>
       <c r="E23">
-        <v>-513.4179999999997</v>
+        <v>-118.8760000000002</v>
       </c>
       <c r="F23">
-        <v>8285.382</v>
+        <v>8679.923999999999</v>
       </c>
       <c r="G23">
         <v>2437.1</v>
@@ -3179,28 +3179,28 @@
         <v>2746.3</v>
       </c>
       <c r="M23">
-        <v>443.267937</v>
+        <v>464.3759339999999</v>
       </c>
       <c r="N23">
-        <v>2303.032063</v>
+        <v>2281.924066</v>
       </c>
       <c r="O23">
-        <v>575.75801575</v>
+        <v>570.4810165000001</v>
       </c>
       <c r="P23">
-        <v>1727.27404725</v>
+        <v>1711.4430495</v>
       </c>
       <c r="Q23">
-        <v>2677.57404725</v>
+        <v>2661.7430495</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1081512197097208</v>
+        <v>0.1087839700619607</v>
       </c>
       <c r="T23">
-        <v>0.9645535388452788</v>
+        <v>0.9743419855557037</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.195575566748019</v>
+        <v>5.913958495532201</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09367899664832935</v>
+        <v>0.09349227972597926</v>
       </c>
       <c r="C24">
-        <v>32185.10989544048</v>
+        <v>31909.45763020439</v>
       </c>
       <c r="D24">
-        <v>38427.93389544048</v>
+        <v>38546.8236302044</v>
       </c>
       <c r="E24">
-        <v>-118.8760000000002</v>
+        <v>275.6660000000011</v>
       </c>
       <c r="F24">
-        <v>8679.923999999999</v>
+        <v>9074.466</v>
       </c>
       <c r="G24">
         <v>2437.1</v>
@@ -3261,28 +3261,28 @@
         <v>2746.3</v>
       </c>
       <c r="M24">
-        <v>464.3759339999999</v>
+        <v>485.483931</v>
       </c>
       <c r="N24">
-        <v>2281.924066</v>
+        <v>2260.816069</v>
       </c>
       <c r="O24">
-        <v>570.4810165000001</v>
+        <v>565.2040172500001</v>
       </c>
       <c r="P24">
-        <v>1711.4430495</v>
+        <v>1695.61205175</v>
       </c>
       <c r="Q24">
-        <v>2661.7430495</v>
+        <v>2645.912051750001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1087839700619607</v>
+        <v>0.1094331554882848</v>
       </c>
       <c r="T24">
-        <v>0.9743419855557037</v>
+        <v>0.9843846776352307</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.913958495532201</v>
+        <v>5.65682986529167</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09349227972597926</v>
+        <v>0.09344956280362919</v>
       </c>
       <c r="C25">
-        <v>31909.45763020439</v>
+        <v>31542.21858811428</v>
       </c>
       <c r="D25">
-        <v>38546.8236302044</v>
+        <v>38574.12658811428</v>
       </c>
       <c r="E25">
-        <v>275.6660000000011</v>
+        <v>670.2080000000005</v>
       </c>
       <c r="F25">
-        <v>9074.466</v>
+        <v>9469.008</v>
       </c>
       <c r="G25">
         <v>2437.1</v>
@@ -3343,45 +3343,45 @@
         <v>2746.3</v>
       </c>
       <c r="M25">
-        <v>485.483931</v>
+        <v>514.1671344</v>
       </c>
       <c r="N25">
-        <v>2260.816069</v>
+        <v>2232.1328656</v>
       </c>
       <c r="O25">
-        <v>565.2040172500001</v>
+        <v>558.0332164</v>
       </c>
       <c r="P25">
-        <v>1695.61205175</v>
+        <v>1674.0996492</v>
       </c>
       <c r="Q25">
-        <v>2645.912051750001</v>
+        <v>2624.3996492</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1094331554882848</v>
+        <v>0.1100994247416174</v>
       </c>
       <c r="T25">
-        <v>0.9843846776352307</v>
+        <v>0.9946916510852717</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>5.65682986529167</v>
+        <v>5.341259322622314</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09344956280362919</v>
+        <v>0.09326884588127912</v>
       </c>
       <c r="C26">
-        <v>31542.21858811428</v>
+        <v>31263.61287978261</v>
       </c>
       <c r="D26">
-        <v>38574.12658811428</v>
+        <v>38690.06287978261</v>
       </c>
       <c r="E26">
-        <v>670.2080000000005</v>
+        <v>1064.75</v>
       </c>
       <c r="F26">
-        <v>9469.008</v>
+        <v>9863.549999999999</v>
       </c>
       <c r="G26">
         <v>2437.1</v>
@@ -3425,28 +3425,28 @@
         <v>2746.3</v>
       </c>
       <c r="M26">
-        <v>514.1671344</v>
+        <v>535.5907649999999</v>
       </c>
       <c r="N26">
-        <v>2232.1328656</v>
+        <v>2210.709235</v>
       </c>
       <c r="O26">
-        <v>558.0332164</v>
+        <v>552.6773087500001</v>
       </c>
       <c r="P26">
-        <v>1674.0996492</v>
+        <v>1658.03192625</v>
       </c>
       <c r="Q26">
-        <v>2624.3996492</v>
+        <v>2608.33192625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1100994247416174</v>
+        <v>0.1107834611750388</v>
       </c>
       <c r="T26">
-        <v>0.9946916510852717</v>
+        <v>1.005273477160647</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.341259322622314</v>
+        <v>5.127608949717422</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09326884588127912</v>
+        <v>0.09308812895892904</v>
       </c>
       <c r="C27">
-        <v>31263.61287978261</v>
+        <v>30985.70617593464</v>
       </c>
       <c r="D27">
-        <v>38690.06287978261</v>
+        <v>38806.69817593464</v>
       </c>
       <c r="E27">
-        <v>1064.75</v>
+        <v>1459.291999999999</v>
       </c>
       <c r="F27">
-        <v>9863.549999999999</v>
+        <v>10258.092</v>
       </c>
       <c r="G27">
         <v>2437.1</v>
@@ -3507,28 +3507,28 @@
         <v>2746.3</v>
       </c>
       <c r="M27">
-        <v>535.5907649999999</v>
+        <v>557.0143955999999</v>
       </c>
       <c r="N27">
-        <v>2210.709235</v>
+        <v>2189.2856044</v>
       </c>
       <c r="O27">
-        <v>552.6773087500001</v>
+        <v>547.3214011</v>
       </c>
       <c r="P27">
-        <v>1658.03192625</v>
+        <v>1641.9642033</v>
       </c>
       <c r="Q27">
-        <v>2608.33192625</v>
+        <v>2592.2642033</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107834611750388</v>
+        <v>0.1114859850796338</v>
       </c>
       <c r="T27">
-        <v>1.005273477160647</v>
+        <v>1.016141298535357</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.127608949717422</v>
+        <v>4.930393220882136</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09308812895892904</v>
+        <v>0.09290741203657896</v>
       </c>
       <c r="C28">
-        <v>30985.70617593464</v>
+        <v>30708.50481735467</v>
       </c>
       <c r="D28">
-        <v>38806.69817593464</v>
+        <v>38924.03881735467</v>
       </c>
       <c r="E28">
-        <v>1459.291999999999</v>
+        <v>1853.834000000001</v>
       </c>
       <c r="F28">
-        <v>10258.092</v>
+        <v>10652.634</v>
       </c>
       <c r="G28">
         <v>2437.1</v>
@@ -3589,28 +3589,28 @@
         <v>2746.3</v>
       </c>
       <c r="M28">
-        <v>557.0143955999999</v>
+        <v>578.4380262</v>
       </c>
       <c r="N28">
-        <v>2189.2856044</v>
+        <v>2167.8619738</v>
       </c>
       <c r="O28">
-        <v>547.3214011</v>
+        <v>541.9654934500001</v>
       </c>
       <c r="P28">
-        <v>1641.9642033</v>
+        <v>1625.89648035</v>
       </c>
       <c r="Q28">
-        <v>2592.2642033</v>
+        <v>2576.19648035</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1114859850796338</v>
+        <v>0.1122077562144917</v>
       </c>
       <c r="T28">
-        <v>1.016141298535357</v>
+        <v>1.02730686844088</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.930393220882136</v>
+        <v>4.747786064553168</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09290741203657896</v>
+        <v>0.09272669511422887</v>
       </c>
       <c r="C29">
-        <v>30708.50481735467</v>
+        <v>30432.01522175068</v>
       </c>
       <c r="D29">
-        <v>38924.03881735467</v>
+        <v>39042.09122175068</v>
       </c>
       <c r="E29">
-        <v>1853.834000000001</v>
+        <v>2248.376</v>
       </c>
       <c r="F29">
-        <v>10652.634</v>
+        <v>11047.176</v>
       </c>
       <c r="G29">
         <v>2437.1</v>
@@ -3671,28 +3671,28 @@
         <v>2746.3</v>
       </c>
       <c r="M29">
-        <v>578.4380262</v>
+        <v>599.8616568</v>
       </c>
       <c r="N29">
-        <v>2167.8619738</v>
+        <v>2146.4383432</v>
       </c>
       <c r="O29">
-        <v>541.9654934500001</v>
+        <v>536.6095858000001</v>
       </c>
       <c r="P29">
-        <v>1625.89648035</v>
+        <v>1609.8287574</v>
       </c>
       <c r="Q29">
-        <v>2576.19648035</v>
+        <v>2560.1287574</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1122077562144917</v>
+        <v>0.1129495765475401</v>
       </c>
       <c r="T29">
-        <v>1.02730686844088</v>
+        <v>1.038782593066002</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.747786064553168</v>
+        <v>4.578222276533412</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09272669511422887</v>
+        <v>0.09254597819187879</v>
       </c>
       <c r="C30">
-        <v>30432.01522175068</v>
+        <v>30156.24388492437</v>
       </c>
       <c r="D30">
-        <v>39042.09122175068</v>
+        <v>39160.86188492437</v>
       </c>
       <c r="E30">
-        <v>2248.376</v>
+        <v>2642.918000000001</v>
       </c>
       <c r="F30">
-        <v>11047.176</v>
+        <v>11441.718</v>
       </c>
       <c r="G30">
         <v>2437.1</v>
@@ -3753,28 +3753,28 @@
         <v>2746.3</v>
       </c>
       <c r="M30">
-        <v>599.8616568</v>
+        <v>621.2852874</v>
       </c>
       <c r="N30">
-        <v>2146.4383432</v>
+        <v>2125.0147126</v>
       </c>
       <c r="O30">
-        <v>536.6095858000001</v>
+        <v>531.25367815</v>
       </c>
       <c r="P30">
-        <v>1609.8287574</v>
+        <v>1593.76103445</v>
       </c>
       <c r="Q30">
-        <v>2560.1287574</v>
+        <v>2544.06103445</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1129495765475401</v>
+        <v>0.1137122932279983</v>
       </c>
       <c r="T30">
-        <v>1.038782593066002</v>
+        <v>1.050581577539718</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.578222276533412</v>
+        <v>4.420352542859845</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09254597819187879</v>
+        <v>0.09236526126952871</v>
       </c>
       <c r="C31">
-        <v>30156.24388492437</v>
+        <v>29881.1973819626</v>
       </c>
       <c r="D31">
-        <v>39160.86188492437</v>
+        <v>39280.3573819626</v>
       </c>
       <c r="E31">
-        <v>2642.918</v>
+        <v>3037.459999999999</v>
       </c>
       <c r="F31">
-        <v>11441.718</v>
+        <v>11836.26</v>
       </c>
       <c r="G31">
         <v>2437.1</v>
@@ -3835,28 +3835,28 @@
         <v>2746.3</v>
       </c>
       <c r="M31">
-        <v>621.2852873999999</v>
+        <v>642.7089179999999</v>
       </c>
       <c r="N31">
-        <v>2125.0147126</v>
+        <v>2103.591082</v>
       </c>
       <c r="O31">
-        <v>531.25367815</v>
+        <v>525.8977705000001</v>
       </c>
       <c r="P31">
-        <v>1593.76103445</v>
+        <v>1577.6933115</v>
       </c>
       <c r="Q31">
-        <v>2544.06103445</v>
+        <v>2527.9933115</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1137122932279983</v>
+        <v>0.1144968018136125</v>
       </c>
       <c r="T31">
-        <v>1.050581577539718</v>
+        <v>1.062717675855541</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.420352542859846</v>
+        <v>4.273007458097852</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09236526126952871</v>
+        <v>0.09241704434717864</v>
       </c>
       <c r="C32">
-        <v>29881.1973819626</v>
+        <v>29452.34036613995</v>
       </c>
       <c r="D32">
-        <v>39280.3573819626</v>
+        <v>39246.04236613995</v>
       </c>
       <c r="E32">
-        <v>3037.459999999999</v>
+        <v>3432.002</v>
       </c>
       <c r="F32">
-        <v>11836.26</v>
+        <v>12230.802</v>
       </c>
       <c r="G32">
         <v>2437.1</v>
@@ -3917,45 +3917,45 @@
         <v>2746.3</v>
       </c>
       <c r="M32">
-        <v>642.7089179999999</v>
+        <v>676.3633506</v>
       </c>
       <c r="N32">
-        <v>2103.591082</v>
+        <v>2069.9366494</v>
       </c>
       <c r="O32">
-        <v>525.8977705000001</v>
+        <v>517.48416235</v>
       </c>
       <c r="P32">
-        <v>1577.6933115</v>
+        <v>1552.45248705</v>
       </c>
       <c r="Q32">
-        <v>2527.9933115</v>
+        <v>2502.75248705</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1144968018136125</v>
+        <v>0.1153040497785198</v>
       </c>
       <c r="T32">
-        <v>1.062717675855541</v>
+        <v>1.07520554513704</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.273007458097852</v>
+        <v>4.060391500461646</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09241704434717864</v>
+        <v>0.09224382742482856</v>
       </c>
       <c r="C33">
-        <v>29452.34036613995</v>
+        <v>29172.81960947688</v>
       </c>
       <c r="D33">
-        <v>39246.04236613995</v>
+        <v>39361.06360947688</v>
       </c>
       <c r="E33">
-        <v>3432.002</v>
+        <v>3826.544</v>
       </c>
       <c r="F33">
-        <v>12230.802</v>
+        <v>12625.344</v>
       </c>
       <c r="G33">
         <v>2437.1</v>
@@ -3999,28 +3999,28 @@
         <v>2746.3</v>
       </c>
       <c r="M33">
-        <v>676.3633506</v>
+        <v>698.1815232</v>
       </c>
       <c r="N33">
-        <v>2069.9366494</v>
+        <v>2048.1184768</v>
       </c>
       <c r="O33">
-        <v>517.48416235</v>
+        <v>512.0296192000001</v>
       </c>
       <c r="P33">
-        <v>1552.45248705</v>
+        <v>1536.0888576</v>
       </c>
       <c r="Q33">
-        <v>2502.75248705</v>
+        <v>2486.3888576</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1153040497785198</v>
+        <v>0.1161350403306302</v>
       </c>
       <c r="T33">
-        <v>1.07520554513704</v>
+        <v>1.088060704691524</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.060391500461646</v>
+        <v>3.933504266072219</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09224382742482856</v>
+        <v>0.09207061050247849</v>
       </c>
       <c r="C34">
-        <v>29172.81960947688</v>
+        <v>28893.97503687643</v>
       </c>
       <c r="D34">
-        <v>39361.06360947688</v>
+        <v>39476.76103687643</v>
       </c>
       <c r="E34">
-        <v>3826.544</v>
+        <v>4221.086000000001</v>
       </c>
       <c r="F34">
-        <v>12625.344</v>
+        <v>13019.886</v>
       </c>
       <c r="G34">
         <v>2437.1</v>
@@ -4081,28 +4081,28 @@
         <v>2746.3</v>
       </c>
       <c r="M34">
-        <v>698.1815232</v>
+        <v>719.9996958</v>
       </c>
       <c r="N34">
-        <v>2048.1184768</v>
+        <v>2026.3003042</v>
       </c>
       <c r="O34">
-        <v>512.0296192000001</v>
+        <v>506.57507605</v>
       </c>
       <c r="P34">
-        <v>1536.0888576</v>
+        <v>1519.72522815</v>
       </c>
       <c r="Q34">
-        <v>2486.3888576</v>
+        <v>2470.02522815</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1161350403306302</v>
+        <v>0.1169908365708634</v>
       </c>
       <c r="T34">
-        <v>1.088060704691524</v>
+        <v>1.101299600352112</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.933504266072219</v>
+        <v>3.814307167100333</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09207061050247849</v>
+        <v>0.09189739358012843</v>
       </c>
       <c r="C35">
-        <v>28893.97503687643</v>
+        <v>28615.81262861836</v>
       </c>
       <c r="D35">
-        <v>39476.76103687643</v>
+        <v>39593.14062861836</v>
       </c>
       <c r="E35">
-        <v>4221.086000000001</v>
+        <v>4615.628000000001</v>
       </c>
       <c r="F35">
-        <v>13019.886</v>
+        <v>13414.428</v>
       </c>
       <c r="G35">
         <v>2437.1</v>
@@ -4163,28 +4163,28 @@
         <v>2746.3</v>
       </c>
       <c r="M35">
-        <v>719.9996958</v>
+        <v>741.8178684000001</v>
       </c>
       <c r="N35">
-        <v>2026.3003042</v>
+        <v>2004.4821316</v>
       </c>
       <c r="O35">
-        <v>506.57507605</v>
+        <v>501.1205329000001</v>
       </c>
       <c r="P35">
-        <v>1519.72522815</v>
+        <v>1503.3615987</v>
       </c>
       <c r="Q35">
-        <v>2470.02522815</v>
+        <v>2453.6615987</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1169908365708634</v>
+        <v>0.1178725660304976</v>
       </c>
       <c r="T35">
-        <v>1.101299600352112</v>
+        <v>1.114939674669081</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.814307167100333</v>
+        <v>3.702121662185618</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09189739358012843</v>
+        <v>0.09172417665777835</v>
       </c>
       <c r="C36">
-        <v>28615.81262861836</v>
+        <v>28338.33843571172</v>
       </c>
       <c r="D36">
-        <v>39593.14062861836</v>
+        <v>39710.20843571173</v>
       </c>
       <c r="E36">
-        <v>4615.628000000001</v>
+        <v>5010.170000000002</v>
       </c>
       <c r="F36">
-        <v>13414.428</v>
+        <v>13808.97</v>
       </c>
       <c r="G36">
         <v>2437.1</v>
@@ -4245,28 +4245,28 @@
         <v>2746.3</v>
       </c>
       <c r="M36">
-        <v>741.8178684000001</v>
+        <v>763.6360410000001</v>
       </c>
       <c r="N36">
-        <v>2004.4821316</v>
+        <v>1982.663959</v>
       </c>
       <c r="O36">
-        <v>501.1205329000001</v>
+        <v>495.66598975</v>
       </c>
       <c r="P36">
-        <v>1503.3615987</v>
+        <v>1486.99796925</v>
       </c>
       <c r="Q36">
-        <v>2453.6615987</v>
+        <v>2437.29796925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1178725660304976</v>
+        <v>0.1187814256273513</v>
       </c>
       <c r="T36">
-        <v>1.114939674669081</v>
+        <v>1.128999443580419</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.702121662185618</v>
+        <v>3.596346757551743</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09172417665777835</v>
+        <v>0.09155095973542825</v>
       </c>
       <c r="C37">
-        <v>28338.33843571172</v>
+        <v>28061.55858094353</v>
       </c>
       <c r="D37">
-        <v>39710.20843571173</v>
+        <v>39827.97058094353</v>
       </c>
       <c r="E37">
-        <v>5010.170000000002</v>
+        <v>5404.712000000001</v>
       </c>
       <c r="F37">
-        <v>13808.97</v>
+        <v>14203.512</v>
       </c>
       <c r="G37">
         <v>2437.1</v>
@@ -4327,28 +4327,28 @@
         <v>2746.3</v>
       </c>
       <c r="M37">
-        <v>763.6360410000001</v>
+        <v>785.4542136000001</v>
       </c>
       <c r="N37">
-        <v>1982.663959</v>
+        <v>1960.8457864</v>
       </c>
       <c r="O37">
-        <v>495.66598975</v>
+        <v>490.2114466</v>
       </c>
       <c r="P37">
-        <v>1486.99796925</v>
+        <v>1470.6343398</v>
       </c>
       <c r="Q37">
-        <v>2437.29796925</v>
+        <v>2420.9343398</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1187814256273513</v>
+        <v>0.1197186870866067</v>
       </c>
       <c r="T37">
-        <v>1.128999443580419</v>
+        <v>1.143498580270236</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.596346757551743</v>
+        <v>3.496448236508639</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09155095973542826</v>
+        <v>0.09137774281307817</v>
       </c>
       <c r="C38">
-        <v>28061.55858094353</v>
+        <v>27785.47925994623</v>
       </c>
       <c r="D38">
-        <v>39827.97058094353</v>
+        <v>39946.43325994623</v>
       </c>
       <c r="E38">
-        <v>5404.712</v>
+        <v>5799.253999999999</v>
       </c>
       <c r="F38">
-        <v>14203.512</v>
+        <v>14598.054</v>
       </c>
       <c r="G38">
         <v>2437.1</v>
@@ -4409,28 +4409,28 @@
         <v>2746.3</v>
       </c>
       <c r="M38">
-        <v>785.4542136</v>
+        <v>807.2723861999999</v>
       </c>
       <c r="N38">
-        <v>1960.8457864</v>
+        <v>1939.0276138</v>
       </c>
       <c r="O38">
-        <v>490.2114466</v>
+        <v>484.7569034500001</v>
       </c>
       <c r="P38">
-        <v>1470.6343398</v>
+        <v>1454.27071035</v>
       </c>
       <c r="Q38">
-        <v>2420.9343398</v>
+        <v>2404.57071035</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1197186870866067</v>
+        <v>0.1206857028779019</v>
       </c>
       <c r="T38">
-        <v>1.143498580270236</v>
+        <v>1.158458007013698</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.496448236508639</v>
+        <v>3.40194963552192</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09137774281307817</v>
+        <v>0.0912045258907281</v>
       </c>
       <c r="C39">
-        <v>27785.47925994623</v>
+        <v>27510.10674228434</v>
       </c>
       <c r="D39">
-        <v>39946.43325994623</v>
+        <v>40065.60274228434</v>
       </c>
       <c r="E39">
-        <v>5799.253999999999</v>
+        <v>6193.796</v>
       </c>
       <c r="F39">
-        <v>14598.054</v>
+        <v>14992.596</v>
       </c>
       <c r="G39">
         <v>2437.1</v>
@@ -4491,28 +4491,28 @@
         <v>2746.3</v>
       </c>
       <c r="M39">
-        <v>807.2723861999999</v>
+        <v>829.0905588000001</v>
       </c>
       <c r="N39">
-        <v>1939.0276138</v>
+        <v>1917.2094412</v>
       </c>
       <c r="O39">
-        <v>484.7569034500001</v>
+        <v>479.3023603</v>
       </c>
       <c r="P39">
-        <v>1454.27071035</v>
+        <v>1437.9070809</v>
       </c>
       <c r="Q39">
-        <v>2404.57071035</v>
+        <v>2388.2070809</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1206857028779019</v>
+        <v>0.1216839127269808</v>
       </c>
       <c r="T39">
-        <v>1.158458007013698</v>
+        <v>1.173899995910175</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.40194963552192</v>
+        <v>3.312424645113448</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0912045258907281</v>
+        <v>0.09103130896837804</v>
       </c>
       <c r="C40">
-        <v>27510.10674228434</v>
+        <v>27235.44737256051</v>
       </c>
       <c r="D40">
-        <v>40065.60274228434</v>
+        <v>40185.48537256051</v>
       </c>
       <c r="E40">
-        <v>6193.796</v>
+        <v>6588.338</v>
       </c>
       <c r="F40">
-        <v>14992.596</v>
+        <v>15387.138</v>
       </c>
       <c r="G40">
         <v>2437.1</v>
@@ -4573,28 +4573,28 @@
         <v>2746.3</v>
       </c>
       <c r="M40">
-        <v>829.0905588000001</v>
+        <v>850.9087314</v>
       </c>
       <c r="N40">
-        <v>1917.2094412</v>
+        <v>1895.3912686</v>
       </c>
       <c r="O40">
-        <v>479.3023603</v>
+        <v>473.8478171500001</v>
       </c>
       <c r="P40">
-        <v>1437.9070809</v>
+        <v>1421.54345145</v>
       </c>
       <c r="Q40">
-        <v>2388.2070809</v>
+        <v>2371.84345145</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1216839127269808</v>
+        <v>0.1227148507678328</v>
       </c>
       <c r="T40">
-        <v>1.173899995910175</v>
+        <v>1.189848279524569</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.312424645113448</v>
+        <v>3.227490679854129</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09103130896837804</v>
+        <v>0.09085809204602796</v>
       </c>
       <c r="C41">
-        <v>27235.44737256051</v>
+        <v>26961.50757154148</v>
       </c>
       <c r="D41">
-        <v>40185.48537256051</v>
+        <v>40306.08757154148</v>
       </c>
       <c r="E41">
-        <v>6588.338</v>
+        <v>6982.880000000001</v>
       </c>
       <c r="F41">
-        <v>15387.138</v>
+        <v>15781.68</v>
       </c>
       <c r="G41">
         <v>2437.1</v>
@@ -4655,28 +4655,28 @@
         <v>2746.3</v>
       </c>
       <c r="M41">
-        <v>850.9087314</v>
+        <v>872.726904</v>
       </c>
       <c r="N41">
-        <v>1895.3912686</v>
+        <v>1873.573096</v>
       </c>
       <c r="O41">
-        <v>473.8478171500001</v>
+        <v>468.393274</v>
       </c>
       <c r="P41">
-        <v>1421.54345145</v>
+        <v>1405.179822</v>
       </c>
       <c r="Q41">
-        <v>2371.84345145</v>
+        <v>2355.479822</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1227148507678328</v>
+        <v>0.1237801534100466</v>
       </c>
       <c r="T41">
-        <v>1.189848279524569</v>
+        <v>1.206328172592776</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.227490679854129</v>
+        <v>3.146803412857775</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09085809204602796</v>
+        <v>0.09068487512367787</v>
       </c>
       <c r="C42">
-        <v>26961.50757154148</v>
+        <v>26688.2938373045</v>
       </c>
       <c r="D42">
-        <v>40306.08757154148</v>
+        <v>40427.41583730451</v>
       </c>
       <c r="E42">
-        <v>6982.880000000001</v>
+        <v>7377.422</v>
       </c>
       <c r="F42">
-        <v>15781.68</v>
+        <v>16176.222</v>
       </c>
       <c r="G42">
         <v>2437.1</v>
@@ -4737,28 +4737,28 @@
         <v>2746.3</v>
       </c>
       <c r="M42">
-        <v>872.726904</v>
+        <v>894.5450766</v>
       </c>
       <c r="N42">
-        <v>1873.573096</v>
+        <v>1851.7549234</v>
       </c>
       <c r="O42">
-        <v>468.393274</v>
+        <v>462.9387308500001</v>
       </c>
       <c r="P42">
-        <v>1405.179822</v>
+        <v>1388.81619255</v>
       </c>
       <c r="Q42">
-        <v>2355.479822</v>
+        <v>2339.11619255</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1237801534100466</v>
+        <v>0.1248815680062337</v>
       </c>
       <c r="T42">
-        <v>1.206328172592776</v>
+        <v>1.223366706103974</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.146803412857775</v>
+        <v>3.070052110105147</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09068487512367787</v>
+        <v>0.09129915820132779</v>
       </c>
       <c r="C43">
-        <v>26688.2938373045</v>
+        <v>25866.74579556095</v>
       </c>
       <c r="D43">
-        <v>40427.41583730451</v>
+        <v>40000.40979556095</v>
       </c>
       <c r="E43">
-        <v>7377.422</v>
+        <v>7771.964</v>
       </c>
       <c r="F43">
-        <v>16176.222</v>
+        <v>16570.764</v>
       </c>
       <c r="G43">
         <v>2437.1</v>
@@ -4819,45 +4819,45 @@
         <v>2746.3</v>
       </c>
       <c r="M43">
-        <v>894.5450766</v>
+        <v>957.7901592000001</v>
       </c>
       <c r="N43">
-        <v>1851.7549234</v>
+        <v>1788.5098408</v>
       </c>
       <c r="O43">
-        <v>462.9387308500001</v>
+        <v>447.1274602</v>
       </c>
       <c r="P43">
-        <v>1388.81619255</v>
+        <v>1341.3823806</v>
       </c>
       <c r="Q43">
-        <v>2339.11619255</v>
+        <v>2291.6823806</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1248815680062337</v>
+        <v>0.1260209624160824</v>
       </c>
       <c r="T43">
-        <v>1.223366706103974</v>
+        <v>1.240992775253488</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.070052110105147</v>
+        <v>2.867329522673175</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09129915820132781</v>
+        <v>0.09114469127897772</v>
       </c>
       <c r="C44">
-        <v>25866.74579556094</v>
+        <v>25578.72705175856</v>
       </c>
       <c r="D44">
-        <v>40000.40979556094</v>
+        <v>40106.93305175856</v>
       </c>
       <c r="E44">
-        <v>7771.964</v>
+        <v>8166.505999999998</v>
       </c>
       <c r="F44">
-        <v>16570.764</v>
+        <v>16965.306</v>
       </c>
       <c r="G44">
         <v>2437.1</v>
@@ -4901,28 +4901,28 @@
         <v>2746.3</v>
       </c>
       <c r="M44">
-        <v>957.7901592000001</v>
+        <v>980.5946867999999</v>
       </c>
       <c r="N44">
-        <v>1788.5098408</v>
+        <v>1765.7053132</v>
       </c>
       <c r="O44">
-        <v>447.1274602</v>
+        <v>441.4263283000001</v>
       </c>
       <c r="P44">
-        <v>1341.3823806</v>
+        <v>1324.2789849</v>
       </c>
       <c r="Q44">
-        <v>2291.6823806</v>
+        <v>2274.5789849</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1260209624160824</v>
+        <v>0.1272003355771539</v>
       </c>
       <c r="T44">
-        <v>1.240992775253488</v>
+        <v>1.259237302969652</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.867329522673175</v>
+        <v>2.800647440750543</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09114469127897772</v>
+        <v>0.09099022435662765</v>
       </c>
       <c r="C45">
-        <v>25578.72705175856</v>
+        <v>25291.27717727902</v>
       </c>
       <c r="D45">
-        <v>40106.93305175856</v>
+        <v>40214.02517727902</v>
       </c>
       <c r="E45">
-        <v>8166.505999999998</v>
+        <v>8561.047999999999</v>
       </c>
       <c r="F45">
-        <v>16965.306</v>
+        <v>17359.848</v>
       </c>
       <c r="G45">
         <v>2437.1</v>
@@ -4983,28 +4983,28 @@
         <v>2746.3</v>
       </c>
       <c r="M45">
-        <v>980.5946867999999</v>
+        <v>1003.3992144</v>
       </c>
       <c r="N45">
-        <v>1765.7053132</v>
+        <v>1742.9007856</v>
       </c>
       <c r="O45">
-        <v>441.4263283000001</v>
+        <v>435.7251964000001</v>
       </c>
       <c r="P45">
-        <v>1324.2789849</v>
+        <v>1307.1755892</v>
       </c>
       <c r="Q45">
-        <v>2274.5789849</v>
+        <v>2257.4755892</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1272003355771539</v>
+        <v>0.1284218292082636</v>
       </c>
       <c r="T45">
-        <v>1.259237302969652</v>
+        <v>1.278133420961394</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.800647440750543</v>
+        <v>2.736996362551667</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09099022435662765</v>
+        <v>0.09083575743427756</v>
       </c>
       <c r="C46">
-        <v>25291.27717727902</v>
+        <v>25004.40074124739</v>
       </c>
       <c r="D46">
-        <v>40214.02517727902</v>
+        <v>40321.6907412474</v>
       </c>
       <c r="E46">
-        <v>8561.047999999999</v>
+        <v>8955.59</v>
       </c>
       <c r="F46">
-        <v>17359.848</v>
+        <v>17754.39</v>
       </c>
       <c r="G46">
         <v>2437.1</v>
@@ -5065,28 +5065,28 @@
         <v>2746.3</v>
       </c>
       <c r="M46">
-        <v>1003.3992144</v>
+        <v>1026.203742</v>
       </c>
       <c r="N46">
-        <v>1742.9007856</v>
+        <v>1720.096258</v>
       </c>
       <c r="O46">
-        <v>435.7251964000001</v>
+        <v>430.0240645</v>
       </c>
       <c r="P46">
-        <v>1307.1755892</v>
+        <v>1290.0721935</v>
       </c>
       <c r="Q46">
-        <v>2257.4755892</v>
+        <v>2240.3721935</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1284218292082636</v>
+        <v>0.1296877407895956</v>
       </c>
       <c r="T46">
-        <v>1.278133420961394</v>
+        <v>1.297716670516471</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.736996362551667</v>
+        <v>2.67617422116163</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09083575743427756</v>
+        <v>0.09068129051192747</v>
       </c>
       <c r="C47">
-        <v>25004.40074124739</v>
+        <v>24718.10236185199</v>
       </c>
       <c r="D47">
-        <v>40321.6907412474</v>
+        <v>40429.93436185199</v>
       </c>
       <c r="E47">
-        <v>8955.59</v>
+        <v>9350.132000000001</v>
       </c>
       <c r="F47">
-        <v>17754.39</v>
+        <v>18148.932</v>
       </c>
       <c r="G47">
         <v>2437.1</v>
@@ -5147,28 +5147,28 @@
         <v>2746.3</v>
       </c>
       <c r="M47">
-        <v>1026.203742</v>
+        <v>1049.0082696</v>
       </c>
       <c r="N47">
-        <v>1720.096258</v>
+        <v>1697.2917304</v>
       </c>
       <c r="O47">
-        <v>430.0240645</v>
+        <v>424.3229326</v>
       </c>
       <c r="P47">
-        <v>1290.0721935</v>
+        <v>1272.9687978</v>
       </c>
       <c r="Q47">
-        <v>2240.3721935</v>
+        <v>2223.2687978</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1296877407895956</v>
+        <v>0.1310005379850509</v>
       </c>
       <c r="T47">
-        <v>1.297716670516471</v>
+        <v>1.318025225610626</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.67617422116163</v>
+        <v>2.617996520701594</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09068129051192747</v>
+        <v>0.09052682358957742</v>
       </c>
       <c r="C48">
-        <v>24718.10236185199</v>
+        <v>24432.38670700472</v>
       </c>
       <c r="D48">
-        <v>40429.93436185199</v>
+        <v>40538.76070700472</v>
       </c>
       <c r="E48">
-        <v>9350.132000000001</v>
+        <v>9744.673999999999</v>
       </c>
       <c r="F48">
-        <v>18148.932</v>
+        <v>18543.474</v>
       </c>
       <c r="G48">
         <v>2437.1</v>
@@ -5229,28 +5229,28 @@
         <v>2746.3</v>
       </c>
       <c r="M48">
-        <v>1049.0082696</v>
+        <v>1071.8127972</v>
       </c>
       <c r="N48">
-        <v>1697.2917304</v>
+        <v>1674.4872028</v>
       </c>
       <c r="O48">
-        <v>424.3229326</v>
+        <v>418.6218007000001</v>
       </c>
       <c r="P48">
-        <v>1272.9687978</v>
+        <v>1255.8654021</v>
       </c>
       <c r="Q48">
-        <v>2223.2687978</v>
+        <v>2206.1654021</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1310005379850509</v>
+        <v>0.1323628746973159</v>
       </c>
       <c r="T48">
-        <v>1.318025225610626</v>
+        <v>1.339100141274371</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.617996520701594</v>
+        <v>2.562294467069646</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09052682358957742</v>
+        <v>0.09037235666722732</v>
       </c>
       <c r="C49">
-        <v>24432.38670700472</v>
+        <v>24147.2584950122</v>
       </c>
       <c r="D49">
-        <v>40538.76070700472</v>
+        <v>40648.1744950122</v>
       </c>
       <c r="E49">
-        <v>9744.673999999999</v>
+        <v>10139.216</v>
       </c>
       <c r="F49">
-        <v>18543.474</v>
+        <v>18938.016</v>
       </c>
       <c r="G49">
         <v>2437.1</v>
@@ -5311,28 +5311,28 @@
         <v>2746.3</v>
       </c>
       <c r="M49">
-        <v>1071.8127972</v>
+        <v>1094.6173248</v>
       </c>
       <c r="N49">
-        <v>1674.4872028</v>
+        <v>1651.6826752</v>
       </c>
       <c r="O49">
-        <v>418.6218007000001</v>
+        <v>412.9206688</v>
       </c>
       <c r="P49">
-        <v>1255.8654021</v>
+        <v>1238.7620064</v>
       </c>
       <c r="Q49">
-        <v>2206.1654021</v>
+        <v>2189.0620064</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1323628746973159</v>
+        <v>0.1337776089754372</v>
       </c>
       <c r="T49">
-        <v>1.339100141274371</v>
+        <v>1.360985630617491</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.562294467069646</v>
+        <v>2.508913332339028</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09037235666722732</v>
+        <v>0.09150413974487724</v>
       </c>
       <c r="C50">
-        <v>24147.2584950122</v>
+        <v>22964.46332547345</v>
       </c>
       <c r="D50">
-        <v>40648.1744950122</v>
+        <v>39859.92132547345</v>
       </c>
       <c r="E50">
-        <v>10139.216</v>
+        <v>10533.758</v>
       </c>
       <c r="F50">
-        <v>18938.016</v>
+        <v>19332.558</v>
       </c>
       <c r="G50">
         <v>2437.1</v>
@@ -5393,45 +5393,45 @@
         <v>2746.3</v>
       </c>
       <c r="M50">
-        <v>1094.6173248</v>
+        <v>1185.0858054</v>
       </c>
       <c r="N50">
-        <v>1651.6826752</v>
+        <v>1561.2141946</v>
       </c>
       <c r="O50">
-        <v>412.9206688</v>
+        <v>390.3035486500001</v>
       </c>
       <c r="P50">
-        <v>1238.7620064</v>
+        <v>1170.91064595</v>
       </c>
       <c r="Q50">
-        <v>2189.0620064</v>
+        <v>2121.21064595</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1337776089754372</v>
+        <v>0.1352478230291711</v>
       </c>
       <c r="T50">
-        <v>1.360985630617491</v>
+        <v>1.383729374444655</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.508913332339028</v>
+        <v>2.317384941652429</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09150413974487724</v>
+        <v>0.09137592282252718</v>
       </c>
       <c r="C51">
-        <v>22964.46332547345</v>
+        <v>22657.68168871546</v>
       </c>
       <c r="D51">
-        <v>39859.92132547345</v>
+        <v>39947.68168871546</v>
       </c>
       <c r="E51">
-        <v>10533.758</v>
+        <v>10928.3</v>
       </c>
       <c r="F51">
-        <v>19332.558</v>
+        <v>19727.1</v>
       </c>
       <c r="G51">
         <v>2437.1</v>
@@ -5475,28 +5475,28 @@
         <v>2746.3</v>
       </c>
       <c r="M51">
-        <v>1185.0858054</v>
+        <v>1209.27123</v>
       </c>
       <c r="N51">
-        <v>1561.2141946</v>
+        <v>1537.02877</v>
       </c>
       <c r="O51">
-        <v>390.3035486500001</v>
+        <v>384.2571925000001</v>
       </c>
       <c r="P51">
-        <v>1170.91064595</v>
+        <v>1152.7715775</v>
       </c>
       <c r="Q51">
-        <v>2121.21064595</v>
+        <v>2103.0715775</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1352478230291711</v>
+        <v>0.1367768456450544</v>
       </c>
       <c r="T51">
-        <v>1.383729374444655</v>
+        <v>1.407382868024906</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.317384941652429</v>
+        <v>2.27103724281938</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09137592282252718</v>
+        <v>0.0923187059001771</v>
       </c>
       <c r="C52">
-        <v>22657.68168871546</v>
+        <v>21626.71742626483</v>
       </c>
       <c r="D52">
-        <v>39947.68168871546</v>
+        <v>39311.25942626483</v>
       </c>
       <c r="E52">
-        <v>10928.3</v>
+        <v>11322.842</v>
       </c>
       <c r="F52">
-        <v>19727.1</v>
+        <v>20121.642</v>
       </c>
       <c r="G52">
         <v>2437.1</v>
@@ -5557,45 +5557,45 @@
         <v>2746.3</v>
       </c>
       <c r="M52">
-        <v>1209.27123</v>
+        <v>1289.7972522</v>
       </c>
       <c r="N52">
-        <v>1537.02877</v>
+        <v>1456.5027478</v>
       </c>
       <c r="O52">
-        <v>384.2571925000001</v>
+        <v>364.12568695</v>
       </c>
       <c r="P52">
-        <v>1152.7715775</v>
+        <v>1092.37706085</v>
       </c>
       <c r="Q52">
-        <v>2103.0715775</v>
+        <v>2042.67706085</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1367768456450544</v>
+        <v>0.1383682773473002</v>
       </c>
       <c r="T52">
-        <v>1.407382868024906</v>
+        <v>1.432001810322717</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.27103724281938</v>
+        <v>2.129249380331406</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0923187059001771</v>
+        <v>0.09221148897782702</v>
       </c>
       <c r="C53">
-        <v>21626.71742626483</v>
+        <v>21303.52803526956</v>
       </c>
       <c r="D53">
-        <v>39311.25942626483</v>
+        <v>39382.61203526956</v>
       </c>
       <c r="E53">
-        <v>11322.842</v>
+        <v>11717.384</v>
       </c>
       <c r="F53">
-        <v>20121.642</v>
+        <v>20516.184</v>
       </c>
       <c r="G53">
         <v>2437.1</v>
@@ -5639,28 +5639,28 @@
         <v>2746.3</v>
       </c>
       <c r="M53">
-        <v>1289.7972522</v>
+        <v>1315.0873944</v>
       </c>
       <c r="N53">
-        <v>1456.5027478</v>
+        <v>1431.2126056</v>
       </c>
       <c r="O53">
-        <v>364.12568695</v>
+        <v>357.8031514</v>
       </c>
       <c r="P53">
-        <v>1092.37706085</v>
+        <v>1073.4094542</v>
       </c>
       <c r="Q53">
-        <v>2042.67706085</v>
+        <v>2023.7094542</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1383682773473002</v>
+        <v>0.1400260187038063</v>
       </c>
       <c r="T53">
-        <v>1.432001810322717</v>
+        <v>1.457646541882938</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.129249380331406</v>
+        <v>2.088302276863494</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09221148897782702</v>
+        <v>0.09210427205547696</v>
       </c>
       <c r="C54">
-        <v>21303.52803526956</v>
+        <v>20980.59813494205</v>
       </c>
       <c r="D54">
-        <v>39382.61203526956</v>
+        <v>39454.22413494205</v>
       </c>
       <c r="E54">
-        <v>11717.384</v>
+        <v>12111.926</v>
       </c>
       <c r="F54">
-        <v>20516.184</v>
+        <v>20910.726</v>
       </c>
       <c r="G54">
         <v>2437.1</v>
@@ -5721,28 +5721,28 @@
         <v>2746.3</v>
       </c>
       <c r="M54">
-        <v>1315.0873944</v>
+        <v>1340.3775366</v>
       </c>
       <c r="N54">
-        <v>1431.2126056</v>
+        <v>1405.9224634</v>
       </c>
       <c r="O54">
-        <v>357.8031514</v>
+        <v>351.48061585</v>
       </c>
       <c r="P54">
-        <v>1073.4094542</v>
+        <v>1054.44184755</v>
       </c>
       <c r="Q54">
-        <v>2023.7094542</v>
+        <v>2004.74184755</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1400260187038063</v>
+        <v>0.1417543022456956</v>
       </c>
       <c r="T54">
-        <v>1.457646541882938</v>
+        <v>1.484382538615934</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.088302276863494</v>
+        <v>2.048900347111353</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09210427205547696</v>
+        <v>0.09199705513312686</v>
       </c>
       <c r="C55">
-        <v>20980.59813494205</v>
+        <v>20657.92914340995</v>
       </c>
       <c r="D55">
-        <v>39454.22413494205</v>
+        <v>39526.09714340996</v>
       </c>
       <c r="E55">
-        <v>12111.926</v>
+        <v>12506.468</v>
       </c>
       <c r="F55">
-        <v>20910.726</v>
+        <v>21305.268</v>
       </c>
       <c r="G55">
         <v>2437.1</v>
@@ -5803,28 +5803,28 @@
         <v>2746.3</v>
       </c>
       <c r="M55">
-        <v>1340.3775366</v>
+        <v>1365.6676788</v>
       </c>
       <c r="N55">
-        <v>1405.9224634</v>
+        <v>1380.6323212</v>
       </c>
       <c r="O55">
-        <v>351.48061585</v>
+        <v>345.1580803</v>
       </c>
       <c r="P55">
-        <v>1054.44184755</v>
+        <v>1035.4742409</v>
       </c>
       <c r="Q55">
-        <v>2004.74184755</v>
+        <v>1985.7742409</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1417543022456956</v>
+        <v>0.1435577285502758</v>
       </c>
       <c r="T55">
-        <v>1.484382538615934</v>
+        <v>1.512280969989495</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.048900347111353</v>
+        <v>2.010957748090772</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09199705513312686</v>
+        <v>0.09510733821077678</v>
       </c>
       <c r="C56">
-        <v>20657.92914340995</v>
+        <v>18279.44893602837</v>
       </c>
       <c r="D56">
-        <v>39526.09714340996</v>
+        <v>37542.15893602837</v>
       </c>
       <c r="E56">
-        <v>12506.468</v>
+        <v>12901.01</v>
       </c>
       <c r="F56">
-        <v>21305.268</v>
+        <v>21699.81</v>
       </c>
       <c r="G56">
         <v>2437.1</v>
@@ -5885,45 +5885,45 @@
         <v>2746.3</v>
       </c>
       <c r="M56">
-        <v>1365.6676788</v>
+        <v>1560.216339</v>
       </c>
       <c r="N56">
-        <v>1380.6323212</v>
+        <v>1186.083661</v>
       </c>
       <c r="O56">
-        <v>345.1580803</v>
+        <v>296.52091525</v>
       </c>
       <c r="P56">
-        <v>1035.4742409</v>
+        <v>889.56274575</v>
       </c>
       <c r="Q56">
-        <v>1985.7742409</v>
+        <v>1839.86274575</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1435577285502758</v>
+        <v>0.1454413071350595</v>
       </c>
       <c r="T56">
-        <v>1.512280969989495</v>
+        <v>1.541419331646325</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.010957748090772</v>
+        <v>1.760204614803742</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09510733821077678</v>
+        <v>0.0966966212884267</v>
       </c>
       <c r="C57">
-        <v>18279.44893602837</v>
+        <v>16946.12082726933</v>
       </c>
       <c r="D57">
-        <v>37542.15893602837</v>
+        <v>36603.37282726933</v>
       </c>
       <c r="E57">
-        <v>12901.01</v>
+        <v>13295.552</v>
       </c>
       <c r="F57">
-        <v>21699.81</v>
+        <v>22094.352</v>
       </c>
       <c r="G57">
         <v>2437.1</v>
@@ -5967,45 +5967,45 @@
         <v>2746.3</v>
       </c>
       <c r="M57">
-        <v>1560.216339</v>
+        <v>1674.7518816</v>
       </c>
       <c r="N57">
-        <v>1186.083661</v>
+        <v>1071.5481184</v>
       </c>
       <c r="O57">
-        <v>296.52091525</v>
+        <v>267.8870296</v>
       </c>
       <c r="P57">
-        <v>889.56274575</v>
+        <v>803.6610888</v>
       </c>
       <c r="Q57">
-        <v>1839.86274575</v>
+        <v>1753.9610888</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1454413071350595</v>
+        <v>0.1474105029282425</v>
       </c>
       <c r="T57">
-        <v>1.541419331646325</v>
+        <v>1.571882164287557</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.760204614803742</v>
+        <v>1.639824997465463</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0966966212884267</v>
+        <v>0.09667715436607663</v>
       </c>
       <c r="C58">
-        <v>16946.12082726933</v>
+        <v>16562.79378386916</v>
       </c>
       <c r="D58">
-        <v>36603.37282726933</v>
+        <v>36614.58778386916</v>
       </c>
       <c r="E58">
-        <v>13295.552</v>
+        <v>13690.094</v>
       </c>
       <c r="F58">
-        <v>22094.352</v>
+        <v>22488.894</v>
       </c>
       <c r="G58">
         <v>2437.1</v>
@@ -6049,28 +6049,28 @@
         <v>2746.3</v>
       </c>
       <c r="M58">
-        <v>1674.7518816</v>
+        <v>1704.6581652</v>
       </c>
       <c r="N58">
-        <v>1071.5481184</v>
+        <v>1041.6418348</v>
       </c>
       <c r="O58">
-        <v>267.8870296</v>
+        <v>260.4104587</v>
       </c>
       <c r="P58">
-        <v>803.6610888</v>
+        <v>781.2313761</v>
       </c>
       <c r="Q58">
-        <v>1753.9610888</v>
+        <v>1731.5313761</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1474105029282425</v>
+        <v>0.149471289223434</v>
       </c>
       <c r="T58">
-        <v>1.571882164287557</v>
+        <v>1.60376187286559</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.639824997465463</v>
+        <v>1.611056137860806</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09667715436607663</v>
+        <v>0.09665768744372655</v>
       </c>
       <c r="C59">
-        <v>16562.79378386916</v>
+        <v>16179.47361490651</v>
       </c>
       <c r="D59">
-        <v>36614.58778386916</v>
+        <v>36625.80961490652</v>
       </c>
       <c r="E59">
-        <v>13690.094</v>
+        <v>14084.636</v>
       </c>
       <c r="F59">
-        <v>22488.894</v>
+        <v>22883.436</v>
       </c>
       <c r="G59">
         <v>2437.1</v>
@@ -6131,28 +6131,28 @@
         <v>2746.3</v>
       </c>
       <c r="M59">
-        <v>1704.6581652</v>
+        <v>1734.5644488</v>
       </c>
       <c r="N59">
-        <v>1041.6418348</v>
+        <v>1011.7355512</v>
       </c>
       <c r="O59">
-        <v>260.4104587</v>
+        <v>252.9338878</v>
       </c>
       <c r="P59">
-        <v>781.2313761</v>
+        <v>758.8016633999999</v>
       </c>
       <c r="Q59">
-        <v>1731.5313761</v>
+        <v>1709.1016634</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.149471289223434</v>
+        <v>0.1516302081993489</v>
       </c>
       <c r="T59">
-        <v>1.60376187286559</v>
+        <v>1.637159662804482</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.611056137860806</v>
+        <v>1.583279307897689</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09665768744372655</v>
+        <v>0.09663822052137647</v>
       </c>
       <c r="C60">
-        <v>16179.47361490652</v>
+        <v>15796.16032670408</v>
       </c>
       <c r="D60">
-        <v>36625.80961490652</v>
+        <v>36637.03832670407</v>
       </c>
       <c r="E60">
-        <v>14084.636</v>
+        <v>14479.178</v>
       </c>
       <c r="F60">
-        <v>22883.436</v>
+        <v>23277.978</v>
       </c>
       <c r="G60">
         <v>2437.1</v>
@@ -6213,28 +6213,28 @@
         <v>2746.3</v>
       </c>
       <c r="M60">
-        <v>1734.5644488</v>
+        <v>1764.4707324</v>
       </c>
       <c r="N60">
-        <v>1011.7355512</v>
+        <v>981.8292676000003</v>
       </c>
       <c r="O60">
-        <v>252.9338878</v>
+        <v>245.4573169000001</v>
       </c>
       <c r="P60">
-        <v>758.8016634000001</v>
+        <v>736.3719507000003</v>
       </c>
       <c r="Q60">
-        <v>1709.1016634</v>
+        <v>1686.6719507</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1516302081993489</v>
+        <v>0.1538944402960402</v>
       </c>
       <c r="T60">
-        <v>1.637159662804482</v>
+        <v>1.672186613228198</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.583279307897689</v>
+        <v>1.556444065390949</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09663822052137647</v>
+        <v>0.0966187535990264</v>
       </c>
       <c r="C61">
-        <v>15796.16032670408</v>
+        <v>15412.85392559226</v>
       </c>
       <c r="D61">
-        <v>36637.03832670407</v>
+        <v>36648.27392559226</v>
       </c>
       <c r="E61">
-        <v>14479.178</v>
+        <v>14873.72</v>
       </c>
       <c r="F61">
-        <v>23277.978</v>
+        <v>23672.52</v>
       </c>
       <c r="G61">
         <v>2437.1</v>
@@ -6295,28 +6295,28 @@
         <v>2746.3</v>
       </c>
       <c r="M61">
-        <v>1764.4707324</v>
+        <v>1794.377016</v>
       </c>
       <c r="N61">
-        <v>981.8292676000003</v>
+        <v>951.9229840000003</v>
       </c>
       <c r="O61">
-        <v>245.4573169000001</v>
+        <v>237.9807460000001</v>
       </c>
       <c r="P61">
-        <v>736.3719507000003</v>
+        <v>713.9422380000002</v>
       </c>
       <c r="Q61">
-        <v>1686.6719507</v>
+        <v>1664.242238</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1538944402960402</v>
+        <v>0.156271883997566</v>
       </c>
       <c r="T61">
-        <v>1.672186613228198</v>
+        <v>1.7089649111731</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.556444065390949</v>
+        <v>1.530503330967766</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0966187535990264</v>
+        <v>0.09659928667667633</v>
       </c>
       <c r="C62">
-        <v>15412.85392559226</v>
+        <v>15029.55441790928</v>
       </c>
       <c r="D62">
-        <v>36648.27392559226</v>
+        <v>36659.51641790928</v>
       </c>
       <c r="E62">
-        <v>14873.72</v>
+        <v>15268.262</v>
       </c>
       <c r="F62">
-        <v>23672.52</v>
+        <v>24067.062</v>
       </c>
       <c r="G62">
         <v>2437.1</v>
@@ -6377,28 +6377,28 @@
         <v>2746.3</v>
       </c>
       <c r="M62">
-        <v>1794.377016</v>
+        <v>1824.2832996</v>
       </c>
       <c r="N62">
-        <v>951.9229840000003</v>
+        <v>922.0167004000002</v>
       </c>
       <c r="O62">
-        <v>237.9807460000001</v>
+        <v>230.5041751000001</v>
       </c>
       <c r="P62">
-        <v>713.9422380000002</v>
+        <v>691.5125253000001</v>
       </c>
       <c r="Q62">
-        <v>1664.242238</v>
+        <v>1641.8125253</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.156271883997566</v>
+        <v>0.1587712478889136</v>
       </c>
       <c r="T62">
-        <v>1.7089649111731</v>
+        <v>1.747629275679279</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.530503330967766</v>
+        <v>1.505413112427311</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09659928667667633</v>
+        <v>0.1178930831256175</v>
       </c>
       <c r="C63">
-        <v>15029.55441790928</v>
+        <v>5424.37813434282</v>
       </c>
       <c r="D63">
-        <v>36659.51641790928</v>
+        <v>27448.88213434282</v>
       </c>
       <c r="E63">
-        <v>15268.262</v>
+        <v>15662.804</v>
       </c>
       <c r="F63">
-        <v>24067.062</v>
+        <v>24461.604</v>
       </c>
       <c r="G63">
         <v>2437.1</v>
@@ -6459,45 +6459,45 @@
         <v>2746.3</v>
       </c>
       <c r="M63">
-        <v>1824.2832996</v>
+        <v>2901.1462344</v>
       </c>
       <c r="N63">
-        <v>922.0167004000002</v>
+        <v>-154.8462344</v>
       </c>
       <c r="O63">
-        <v>230.5041751000001</v>
+        <v>-38.71155859999999</v>
       </c>
       <c r="P63">
-        <v>691.5125253000001</v>
+        <v>-116.1346758</v>
       </c>
       <c r="Q63">
-        <v>1641.8125253</v>
+        <v>834.1653242</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1587712478889136</v>
+        <v>0.1625339631545288</v>
       </c>
       <c r="T63">
-        <v>1.747629275679279</v>
+        <v>1.805837284151492</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.25</v>
+        <v>0.2366564607667886</v>
       </c>
       <c r="W63">
-        <v>0.05685</v>
+        <v>0.09053254375305889</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.505413112427311</v>
+        <v>0.9466258430671544</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1178930831256175</v>
+        <v>0.1186210831256174</v>
       </c>
       <c r="C64">
-        <v>5424.37813434282</v>
+        <v>4796.064832622356</v>
       </c>
       <c r="D64">
-        <v>27448.88213434282</v>
+        <v>27215.11083262235</v>
       </c>
       <c r="E64">
-        <v>15662.804</v>
+        <v>16057.346</v>
       </c>
       <c r="F64">
-        <v>24461.604</v>
+        <v>24856.146</v>
       </c>
       <c r="G64">
         <v>2437.1</v>
@@ -6541,37 +6541,37 @@
         <v>2746.3</v>
       </c>
       <c r="M64">
-        <v>2901.1462344</v>
+        <v>2947.9389156</v>
       </c>
       <c r="N64">
-        <v>-154.8462344</v>
+        <v>-201.6389155999996</v>
       </c>
       <c r="O64">
-        <v>-38.71155859999999</v>
+        <v>-50.40972889999989</v>
       </c>
       <c r="P64">
-        <v>-116.1346758</v>
+        <v>-151.2291866999997</v>
       </c>
       <c r="Q64">
-        <v>834.1653242</v>
+        <v>799.0708133000003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1625339631545288</v>
+        <v>0.1656889351316782</v>
       </c>
       <c r="T64">
-        <v>1.805837284151492</v>
+        <v>1.854643697236667</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.2366564607667886</v>
+        <v>0.2329000090085856</v>
       </c>
       <c r="W64">
-        <v>0.09053254375305889</v>
+        <v>0.09097805893158176</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9466258430671544</v>
+        <v>0.9316000360343425</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1186210831256174</v>
+        <v>0.1193490831256175</v>
       </c>
       <c r="C65">
-        <v>4796.064832622356</v>
+        <v>4171.69978113984</v>
       </c>
       <c r="D65">
-        <v>27215.11083262235</v>
+        <v>26985.28778113984</v>
       </c>
       <c r="E65">
-        <v>16057.346</v>
+        <v>16451.888</v>
       </c>
       <c r="F65">
-        <v>24856.146</v>
+        <v>25250.688</v>
       </c>
       <c r="G65">
         <v>2437.1</v>
@@ -6623,37 +6623,37 @@
         <v>2746.3</v>
       </c>
       <c r="M65">
-        <v>2947.9389156</v>
+        <v>2994.7315968</v>
       </c>
       <c r="N65">
-        <v>-201.6389155999996</v>
+        <v>-248.4315968000001</v>
       </c>
       <c r="O65">
-        <v>-50.40972889999989</v>
+        <v>-62.10789920000002</v>
       </c>
       <c r="P65">
-        <v>-151.2291866999997</v>
+        <v>-186.3236976000001</v>
       </c>
       <c r="Q65">
-        <v>799.0708133000003</v>
+        <v>763.9763023999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1656889351316782</v>
+        <v>0.1690191833297804</v>
       </c>
       <c r="T65">
-        <v>1.854643697236667</v>
+        <v>1.906161577715464</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.2329000090085856</v>
+        <v>0.2292609463678264</v>
       </c>
       <c r="W65">
-        <v>0.09097805893158176</v>
+        <v>0.09140965176077578</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9316000360343425</v>
+        <v>0.9170437854713057</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1193490831256175</v>
+        <v>0.1200770831256175</v>
       </c>
       <c r="C66">
-        <v>4171.69978113984</v>
+        <v>3551.183792308799</v>
       </c>
       <c r="D66">
-        <v>26985.28778113984</v>
+        <v>26759.3137923088</v>
       </c>
       <c r="E66">
-        <v>16451.888</v>
+        <v>16846.43</v>
       </c>
       <c r="F66">
-        <v>25250.688</v>
+        <v>25645.23</v>
       </c>
       <c r="G66">
         <v>2437.1</v>
@@ -6705,37 +6705,37 @@
         <v>2746.3</v>
       </c>
       <c r="M66">
-        <v>2994.7315968</v>
+        <v>3041.524278</v>
       </c>
       <c r="N66">
-        <v>-248.4315968000001</v>
+        <v>-295.2242780000001</v>
       </c>
       <c r="O66">
-        <v>-62.10789920000002</v>
+        <v>-73.80606950000004</v>
       </c>
       <c r="P66">
-        <v>-186.3236976000001</v>
+        <v>-221.4182085000001</v>
       </c>
       <c r="Q66">
-        <v>763.9763023999999</v>
+        <v>728.8817914999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1690191833297804</v>
+        <v>0.172539731424917</v>
       </c>
       <c r="T66">
-        <v>1.906161577715464</v>
+        <v>1.960623337078763</v>
       </c>
       <c r="U66">
         <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.2292609463678264</v>
+        <v>0.2257338548852445</v>
       </c>
       <c r="W66">
-        <v>0.09140965176077578</v>
+        <v>0.09182796481061002</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9170437854713057</v>
+        <v>0.9029354195409779</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1200770831256175</v>
+        <v>0.1208050831256175</v>
       </c>
       <c r="C67">
-        <v>3551.183792308799</v>
+        <v>2934.420973327793</v>
       </c>
       <c r="D67">
-        <v>26759.3137923088</v>
+        <v>26537.0929733278</v>
       </c>
       <c r="E67">
-        <v>16846.43</v>
+        <v>17240.972</v>
       </c>
       <c r="F67">
-        <v>25645.23</v>
+        <v>26039.772</v>
       </c>
       <c r="G67">
         <v>2437.1</v>
@@ -6787,37 +6787,37 @@
         <v>2746.3</v>
       </c>
       <c r="M67">
-        <v>3041.524278</v>
+        <v>3088.3169592</v>
       </c>
       <c r="N67">
-        <v>-295.2242780000001</v>
+        <v>-342.0169592000002</v>
       </c>
       <c r="O67">
-        <v>-73.80606950000004</v>
+        <v>-85.50423980000005</v>
       </c>
       <c r="P67">
-        <v>-221.4182085000001</v>
+        <v>-256.5127194000002</v>
       </c>
       <c r="Q67">
-        <v>728.8817914999998</v>
+        <v>693.7872805999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.172539731424917</v>
+        <v>0.1762673705844734</v>
       </c>
       <c r="T67">
-        <v>1.960623337078763</v>
+        <v>2.018288729345785</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2257338548852445</v>
+        <v>0.2223136449627408</v>
       </c>
       <c r="W67">
-        <v>0.09182796481061002</v>
+        <v>0.09223360170741896</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9029354195409779</v>
+        <v>0.889254579850963</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1208050831256175</v>
+        <v>0.1215330831256174</v>
       </c>
       <c r="C68">
-        <v>2934.420973327793</v>
+        <v>2321.318590500632</v>
       </c>
       <c r="D68">
-        <v>26537.0929733278</v>
+        <v>26318.53259050063</v>
       </c>
       <c r="E68">
-        <v>17240.972</v>
+        <v>17635.514</v>
       </c>
       <c r="F68">
-        <v>26039.772</v>
+        <v>26434.314</v>
       </c>
       <c r="G68">
         <v>2437.1</v>
@@ -6869,37 +6869,37 @@
         <v>2746.3</v>
       </c>
       <c r="M68">
-        <v>3088.3169592</v>
+        <v>3135.1096404</v>
       </c>
       <c r="N68">
-        <v>-342.0169592000002</v>
+        <v>-388.8096403999998</v>
       </c>
       <c r="O68">
-        <v>-85.50423980000005</v>
+        <v>-97.20241009999995</v>
       </c>
       <c r="P68">
-        <v>-256.5127194000002</v>
+        <v>-291.6072302999999</v>
       </c>
       <c r="Q68">
-        <v>693.7872805999998</v>
+        <v>658.6927697000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1762673705844734</v>
+        <v>0.1802209272688514</v>
       </c>
       <c r="T68">
-        <v>2.018288729345785</v>
+        <v>2.079448993871415</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2223136449627408</v>
+        <v>0.2189955308588193</v>
       </c>
       <c r="W68">
-        <v>0.09223360170741896</v>
+        <v>0.09262713004014404</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.889254579850963</v>
+        <v>0.8759821234352771</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1215330831256174</v>
+        <v>0.1222610831256175</v>
       </c>
       <c r="C69">
-        <v>2321.318590500632</v>
+        <v>1711.786940206559</v>
       </c>
       <c r="D69">
-        <v>26318.53259050063</v>
+        <v>26103.54294020656</v>
       </c>
       <c r="E69">
-        <v>17635.514</v>
+        <v>18030.056</v>
       </c>
       <c r="F69">
-        <v>26434.314</v>
+        <v>26828.856</v>
       </c>
       <c r="G69">
         <v>2437.1</v>
@@ -6951,37 +6951,37 @@
         <v>2746.3</v>
       </c>
       <c r="M69">
-        <v>3135.1096404</v>
+        <v>3181.9023216</v>
       </c>
       <c r="N69">
-        <v>-388.8096403999998</v>
+        <v>-435.6023215999999</v>
       </c>
       <c r="O69">
-        <v>-97.20241009999995</v>
+        <v>-108.9005804</v>
       </c>
       <c r="P69">
-        <v>-291.6072302999999</v>
+        <v>-326.7017411999999</v>
       </c>
       <c r="Q69">
-        <v>658.6927697000001</v>
+        <v>623.5982588000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1802209272688514</v>
+        <v>0.184421581246003</v>
       </c>
       <c r="T69">
-        <v>2.079448993871415</v>
+        <v>2.144431774929897</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2189955308588193</v>
+        <v>0.2157750083461896</v>
       </c>
       <c r="W69">
-        <v>0.09262713004014404</v>
+        <v>0.09300908401014192</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8759821234352771</v>
+        <v>0.8631000333847584</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1222610831256175</v>
+        <v>0.1229890831256175</v>
       </c>
       <c r="C70">
-        <v>1711.786940206559</v>
+        <v>1105.739226143352</v>
       </c>
       <c r="D70">
-        <v>26103.54294020656</v>
+        <v>25892.03722614335</v>
       </c>
       <c r="E70">
-        <v>18030.056</v>
+        <v>18424.598</v>
       </c>
       <c r="F70">
-        <v>26828.856</v>
+        <v>27223.398</v>
       </c>
       <c r="G70">
         <v>2437.1</v>
@@ -7033,37 +7033,37 @@
         <v>2746.3</v>
       </c>
       <c r="M70">
-        <v>3181.9023216</v>
+        <v>3228.695002800001</v>
       </c>
       <c r="N70">
-        <v>-435.6023215999999</v>
+        <v>-482.3950028000004</v>
       </c>
       <c r="O70">
-        <v>-108.9005804</v>
+        <v>-120.5987507000001</v>
       </c>
       <c r="P70">
-        <v>-326.7017411999999</v>
+        <v>-361.7962521000003</v>
       </c>
       <c r="Q70">
-        <v>623.5982588000001</v>
+        <v>588.5037478999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.184421581246003</v>
+        <v>0.1888932451571644</v>
       </c>
       <c r="T70">
-        <v>2.144431774929897</v>
+        <v>2.213606993476022</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2157750083461896</v>
+        <v>0.2126478343121868</v>
       </c>
       <c r="W70">
-        <v>0.09300908401014192</v>
+        <v>0.09337996685057465</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8631000333847584</v>
+        <v>0.8505913372487472</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1229890831256175</v>
+        <v>0.1237170831256175</v>
       </c>
       <c r="C71">
-        <v>1105.739226143352</v>
+        <v>503.091442490233</v>
       </c>
       <c r="D71">
-        <v>25892.03722614335</v>
+        <v>25683.93144249024</v>
       </c>
       <c r="E71">
-        <v>18424.598</v>
+        <v>18819.14</v>
       </c>
       <c r="F71">
-        <v>27223.398</v>
+        <v>27617.94</v>
       </c>
       <c r="G71">
         <v>2437.1</v>
@@ -7115,37 +7115,37 @@
         <v>2746.3</v>
       </c>
       <c r="M71">
-        <v>3228.695002800001</v>
+        <v>3275.487684000001</v>
       </c>
       <c r="N71">
-        <v>-482.3950028000004</v>
+        <v>-529.1876840000004</v>
       </c>
       <c r="O71">
-        <v>-120.5987507000001</v>
+        <v>-132.2969210000001</v>
       </c>
       <c r="P71">
-        <v>-361.7962521000003</v>
+        <v>-396.8907630000003</v>
       </c>
       <c r="Q71">
-        <v>588.5037478999997</v>
+        <v>553.4092369999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1888932451571644</v>
+        <v>0.1936630199957365</v>
       </c>
       <c r="T71">
-        <v>2.213606993476022</v>
+        <v>2.287393893258557</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2126478343121868</v>
+        <v>0.209610008107727</v>
       </c>
       <c r="W71">
-        <v>0.09337996685057465</v>
+        <v>0.09374025303842358</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8505913372487472</v>
+        <v>0.838440032430908</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1237170831256175</v>
+        <v>0.1244450831256175</v>
       </c>
       <c r="C72">
-        <v>503.091442490233</v>
+        <v>-96.23773733962298</v>
       </c>
       <c r="D72">
-        <v>25683.93144249024</v>
+        <v>25479.14426266038</v>
       </c>
       <c r="E72">
-        <v>18819.14</v>
+        <v>19213.682</v>
       </c>
       <c r="F72">
-        <v>27617.94</v>
+        <v>28012.482</v>
       </c>
       <c r="G72">
         <v>2437.1</v>
@@ -7197,37 +7197,37 @@
         <v>2746.3</v>
       </c>
       <c r="M72">
-        <v>3275.487684000001</v>
+        <v>3322.2803652</v>
       </c>
       <c r="N72">
-        <v>-529.1876840000004</v>
+        <v>-575.9803652000001</v>
       </c>
       <c r="O72">
-        <v>-132.2969210000001</v>
+        <v>-143.9950913</v>
       </c>
       <c r="P72">
-        <v>-396.8907630000003</v>
+        <v>-431.9852739</v>
       </c>
       <c r="Q72">
-        <v>553.4092369999996</v>
+        <v>518.3147260999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1936630199957365</v>
+        <v>0.1987617448231757</v>
       </c>
       <c r="T72">
-        <v>2.287393893258557</v>
+        <v>2.366269544750232</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.209610008107727</v>
+        <v>0.2066577544724069</v>
       </c>
       <c r="W72">
-        <v>0.09374025303842358</v>
+        <v>0.09409039031957256</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.838440032430908</v>
+        <v>0.8266310178896277</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1244450831256174</v>
+        <v>0.1251730831256175</v>
       </c>
       <c r="C73">
-        <v>-96.23773733961207</v>
+        <v>-692.3270666666758</v>
       </c>
       <c r="D73">
-        <v>25479.14426266039</v>
+        <v>25277.59693333332</v>
       </c>
       <c r="E73">
-        <v>19213.682</v>
+        <v>19608.224</v>
       </c>
       <c r="F73">
-        <v>28012.482</v>
+        <v>28407.024</v>
       </c>
       <c r="G73">
         <v>2437.1</v>
@@ -7279,37 +7279,37 @@
         <v>2746.3</v>
       </c>
       <c r="M73">
-        <v>3322.2803652</v>
+        <v>3369.0730464</v>
       </c>
       <c r="N73">
-        <v>-575.9803651999996</v>
+        <v>-622.7730463999997</v>
       </c>
       <c r="O73">
-        <v>-143.9950912999999</v>
+        <v>-155.6932615999999</v>
       </c>
       <c r="P73">
-        <v>-431.9852738999997</v>
+        <v>-467.0797847999997</v>
       </c>
       <c r="Q73">
-        <v>518.3147261000003</v>
+        <v>483.2202152000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1987617448231757</v>
+        <v>0.2042246642811462</v>
       </c>
       <c r="T73">
-        <v>2.36626954475023</v>
+        <v>2.450779171348453</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2066577544724069</v>
+        <v>0.2037875078825124</v>
       </c>
       <c r="W73">
-        <v>0.09409039031957254</v>
+        <v>0.09443080156513403</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8266310178896278</v>
+        <v>0.8151500315300496</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1251730831256175</v>
+        <v>0.1259010831256175</v>
       </c>
       <c r="C74">
-        <v>-692.3270666666758</v>
+        <v>-1285.25282652261</v>
       </c>
       <c r="D74">
-        <v>25277.59693333332</v>
+        <v>25079.21317347739</v>
       </c>
       <c r="E74">
-        <v>19608.224</v>
+        <v>20002.766</v>
       </c>
       <c r="F74">
-        <v>28407.024</v>
+        <v>28801.566</v>
       </c>
       <c r="G74">
         <v>2437.1</v>
@@ -7361,37 +7361,37 @@
         <v>2746.3</v>
       </c>
       <c r="M74">
-        <v>3369.0730464</v>
+        <v>3415.8657276</v>
       </c>
       <c r="N74">
-        <v>-622.7730463999997</v>
+        <v>-669.5657276000002</v>
       </c>
       <c r="O74">
-        <v>-155.6932615999999</v>
+        <v>-167.3914319</v>
       </c>
       <c r="P74">
-        <v>-467.0797847999997</v>
+        <v>-502.1742957000001</v>
       </c>
       <c r="Q74">
-        <v>483.2202152000002</v>
+        <v>448.1257042999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2042246642811462</v>
+        <v>0.2100922444397072</v>
       </c>
       <c r="T74">
-        <v>2.450779171348453</v>
+        <v>2.541548770287284</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2037875078825124</v>
+        <v>0.2009958981854917</v>
       </c>
       <c r="W74">
-        <v>0.09443080156513403</v>
+        <v>0.0947618864752007</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8151500315300496</v>
+        <v>0.8039835927419666</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1259010831256175</v>
+        <v>0.1905796445488032</v>
       </c>
       <c r="C75">
-        <v>-1285.25282652261</v>
+        <v>-11982.77739766168</v>
       </c>
       <c r="D75">
-        <v>25079.21317347739</v>
+        <v>14776.23060233832</v>
       </c>
       <c r="E75">
-        <v>20002.766</v>
+        <v>20397.308</v>
       </c>
       <c r="F75">
-        <v>28801.566</v>
+        <v>29196.108</v>
       </c>
       <c r="G75">
         <v>2437.1</v>
@@ -7443,45 +7443,45 @@
         <v>2746.3</v>
       </c>
       <c r="M75">
-        <v>3415.8657276</v>
+        <v>5862.5784864</v>
       </c>
       <c r="N75">
-        <v>-669.5657276000002</v>
+        <v>-3116.2784864</v>
       </c>
       <c r="O75">
-        <v>-167.3914319</v>
+        <v>-779.0696215999999</v>
       </c>
       <c r="P75">
-        <v>-502.1742957000001</v>
+        <v>-2337.2088648</v>
       </c>
       <c r="Q75">
-        <v>448.1257042999998</v>
+        <v>-1386.9088648</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2100922444397072</v>
+        <v>0.2284210285457948</v>
       </c>
       <c r="T75">
-        <v>2.541548770287284</v>
+        <v>2.825089231156596</v>
       </c>
       <c r="U75">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.2009958981854917</v>
+        <v>0.1171114385236318</v>
       </c>
       <c r="W75">
-        <v>0.0947618864752007</v>
+        <v>0.1772840231444547</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8039835927419666</v>
+        <v>0.4684457540945273</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1905796445488032</v>
+        <v>0.1921296445488032</v>
       </c>
       <c r="C76">
-        <v>-11982.77739766168</v>
+        <v>-12521.37471702793</v>
       </c>
       <c r="D76">
-        <v>14776.23060233832</v>
+        <v>14632.17528297207</v>
       </c>
       <c r="E76">
-        <v>20397.308</v>
+        <v>20791.85</v>
       </c>
       <c r="F76">
-        <v>29196.108</v>
+        <v>29590.65</v>
       </c>
       <c r="G76">
         <v>2437.1</v>
@@ -7525,37 +7525,37 @@
         <v>2746.3</v>
       </c>
       <c r="M76">
-        <v>5862.5784864</v>
+        <v>5941.80252</v>
       </c>
       <c r="N76">
-        <v>-3116.2784864</v>
+        <v>-3195.50252</v>
       </c>
       <c r="O76">
-        <v>-779.0696215999999</v>
+        <v>-798.87563</v>
       </c>
       <c r="P76">
-        <v>-2337.2088648</v>
+        <v>-2396.62689</v>
       </c>
       <c r="Q76">
-        <v>-1386.9088648</v>
+        <v>-1446.32689</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2284210285457948</v>
+        <v>0.2357258696876267</v>
       </c>
       <c r="T76">
-        <v>2.825089231156596</v>
+        <v>2.93809280040286</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1171114385236318</v>
+        <v>0.1155499526766501</v>
       </c>
       <c r="W76">
-        <v>0.1772840231444547</v>
+        <v>0.1775975695025287</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4684457540945273</v>
+        <v>0.4621998107066002</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1921296445488032</v>
+        <v>0.1936796445488032</v>
       </c>
       <c r="C77">
-        <v>-12521.37471702793</v>
+        <v>-13057.19032897294</v>
       </c>
       <c r="D77">
-        <v>14632.17528297207</v>
+        <v>14490.90167102706</v>
       </c>
       <c r="E77">
-        <v>20791.85</v>
+        <v>21186.392</v>
       </c>
       <c r="F77">
-        <v>29590.65</v>
+        <v>29985.192</v>
       </c>
       <c r="G77">
         <v>2437.1</v>
@@ -7607,37 +7607,37 @@
         <v>2746.3</v>
       </c>
       <c r="M77">
-        <v>5941.80252</v>
+        <v>6021.0265536</v>
       </c>
       <c r="N77">
-        <v>-3195.50252</v>
+        <v>-3274.7265536</v>
       </c>
       <c r="O77">
-        <v>-798.87563</v>
+        <v>-818.6816383999999</v>
       </c>
       <c r="P77">
-        <v>-2396.62689</v>
+        <v>-2456.0449152</v>
       </c>
       <c r="Q77">
-        <v>-1446.32689</v>
+        <v>-1505.7449152</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2357258696876267</v>
+        <v>0.2436394475912778</v>
       </c>
       <c r="T77">
-        <v>2.93809280040286</v>
+        <v>3.060513333752979</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1155499526766501</v>
+        <v>0.1140295585624836</v>
       </c>
       <c r="W77">
-        <v>0.1775975695025287</v>
+        <v>0.1779028646406533</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4621998107066002</v>
+        <v>0.4561182342499345</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1936796445488032</v>
+        <v>0.1952296445488031</v>
       </c>
       <c r="C78">
-        <v>-13057.19032897294</v>
+        <v>-13590.30403514443</v>
       </c>
       <c r="D78">
-        <v>14490.90167102706</v>
+        <v>14352.32996485557</v>
       </c>
       <c r="E78">
-        <v>21186.392</v>
+        <v>21580.934</v>
       </c>
       <c r="F78">
-        <v>29985.192</v>
+        <v>30379.734</v>
       </c>
       <c r="G78">
         <v>2437.1</v>
@@ -7689,37 +7689,37 @@
         <v>2746.3</v>
       </c>
       <c r="M78">
-        <v>6021.0265536</v>
+        <v>6100.250587199999</v>
       </c>
       <c r="N78">
-        <v>-3274.7265536</v>
+        <v>-3353.950587199999</v>
       </c>
       <c r="O78">
-        <v>-818.6816383999999</v>
+        <v>-838.4876467999998</v>
       </c>
       <c r="P78">
-        <v>-2456.0449152</v>
+        <v>-2515.462940399999</v>
       </c>
       <c r="Q78">
-        <v>-1505.7449152</v>
+        <v>-1565.162940399999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2436394475912778</v>
+        <v>0.252241162703942</v>
       </c>
       <c r="T78">
-        <v>3.060513333752979</v>
+        <v>3.193579130872674</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1140295585624836</v>
+        <v>0.1125486552045293</v>
       </c>
       <c r="W78">
-        <v>0.1779028646406533</v>
+        <v>0.1782002300349305</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4561182342499345</v>
+        <v>0.4501946208181171</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1952296445488031</v>
+        <v>0.1967796445488032</v>
       </c>
       <c r="C79">
-        <v>-13590.30403514443</v>
+        <v>-14120.79261363618</v>
       </c>
       <c r="D79">
-        <v>14352.32996485557</v>
+        <v>14216.38338636382</v>
       </c>
       <c r="E79">
-        <v>21580.934</v>
+        <v>21975.476</v>
       </c>
       <c r="F79">
-        <v>30379.734</v>
+        <v>30774.276</v>
       </c>
       <c r="G79">
         <v>2437.1</v>
@@ -7771,37 +7771,37 @@
         <v>2746.3</v>
       </c>
       <c r="M79">
-        <v>6100.250587199999</v>
+        <v>6179.4746208</v>
       </c>
       <c r="N79">
-        <v>-3353.950587199999</v>
+        <v>-3433.1746208</v>
       </c>
       <c r="O79">
-        <v>-838.4876467999998</v>
+        <v>-858.2936551999999</v>
       </c>
       <c r="P79">
-        <v>-2515.462940399999</v>
+        <v>-2574.880965599999</v>
       </c>
       <c r="Q79">
-        <v>-1565.162940399999</v>
+        <v>-1624.580965599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.252241162703942</v>
+        <v>0.2616248519177576</v>
       </c>
       <c r="T79">
-        <v>3.193579130872674</v>
+        <v>3.338741818639614</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1125486552045293</v>
+        <v>0.1111057237275481</v>
       </c>
       <c r="W79">
-        <v>0.1782002300349305</v>
+        <v>0.1784899706755083</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4501946208181171</v>
+        <v>0.4444228949101925</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1967796445488032</v>
+        <v>0.1983296445488031</v>
       </c>
       <c r="C80">
-        <v>-14120.79261363618</v>
+        <v>-14648.72996084126</v>
       </c>
       <c r="D80">
-        <v>14216.38338636382</v>
+        <v>14082.98803915874</v>
       </c>
       <c r="E80">
-        <v>21975.476</v>
+        <v>22370.018</v>
       </c>
       <c r="F80">
-        <v>30774.276</v>
+        <v>31168.818</v>
       </c>
       <c r="G80">
         <v>2437.1</v>
@@ -7853,37 +7853,37 @@
         <v>2746.3</v>
       </c>
       <c r="M80">
-        <v>6179.4746208</v>
+        <v>6258.6986544</v>
       </c>
       <c r="N80">
-        <v>-3433.1746208</v>
+        <v>-3512.3986544</v>
       </c>
       <c r="O80">
-        <v>-858.2936551999999</v>
+        <v>-878.0996636</v>
       </c>
       <c r="P80">
-        <v>-2574.880965599999</v>
+        <v>-2634.2989908</v>
       </c>
       <c r="Q80">
-        <v>-1624.580965599999</v>
+        <v>-1683.9989908</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2616248519177576</v>
+        <v>0.2719022258186031</v>
       </c>
       <c r="T80">
-        <v>3.338741818639614</v>
+        <v>3.497729524289119</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1111057237275481</v>
+        <v>0.1096993221613766</v>
       </c>
       <c r="W80">
-        <v>0.1784899706755083</v>
+        <v>0.1787723761099956</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4444228949101925</v>
+        <v>0.4387972886455065</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1983296445488031</v>
+        <v>0.1998796445488032</v>
       </c>
       <c r="C81">
-        <v>-14648.72996084126</v>
+        <v>-15174.18722539332</v>
       </c>
       <c r="D81">
-        <v>14082.98803915874</v>
+        <v>13952.07277460668</v>
       </c>
       <c r="E81">
-        <v>22370.018</v>
+        <v>22764.56</v>
       </c>
       <c r="F81">
-        <v>31168.818</v>
+        <v>31563.36</v>
       </c>
       <c r="G81">
         <v>2437.1</v>
@@ -7935,37 +7935,37 @@
         <v>2746.3</v>
       </c>
       <c r="M81">
-        <v>6258.6986544</v>
+        <v>6337.922688000001</v>
       </c>
       <c r="N81">
-        <v>-3512.3986544</v>
+        <v>-3591.622688</v>
       </c>
       <c r="O81">
-        <v>-878.0996636</v>
+        <v>-897.9056720000001</v>
       </c>
       <c r="P81">
-        <v>-2634.2989908</v>
+        <v>-2693.717016000001</v>
       </c>
       <c r="Q81">
-        <v>-1683.9989908</v>
+        <v>-1743.417016000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2719022258186031</v>
+        <v>0.2832073371095333</v>
       </c>
       <c r="T81">
-        <v>3.497729524289119</v>
+        <v>3.672616000503576</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1096993221613766</v>
+        <v>0.1083280806343594</v>
       </c>
       <c r="W81">
-        <v>0.1787723761099956</v>
+        <v>0.1790477214086206</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4387972886455065</v>
+        <v>0.4333123225374377</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1998796445488032</v>
+        <v>0.2014296445488032</v>
       </c>
       <c r="C82">
-        <v>-15174.18722539332</v>
+        <v>-15697.23293470589</v>
       </c>
       <c r="D82">
-        <v>13952.07277460668</v>
+        <v>13823.56906529411</v>
       </c>
       <c r="E82">
-        <v>22764.56</v>
+        <v>23159.102</v>
       </c>
       <c r="F82">
-        <v>31563.36</v>
+        <v>31957.902</v>
       </c>
       <c r="G82">
         <v>2437.1</v>
@@ -8017,37 +8017,37 @@
         <v>2746.3</v>
       </c>
       <c r="M82">
-        <v>6337.922688000001</v>
+        <v>6417.1467216</v>
       </c>
       <c r="N82">
-        <v>-3591.622688</v>
+        <v>-3670.8467216</v>
       </c>
       <c r="O82">
-        <v>-897.9056720000001</v>
+        <v>-917.7116804</v>
       </c>
       <c r="P82">
-        <v>-2693.717016000001</v>
+        <v>-2753.1350412</v>
       </c>
       <c r="Q82">
-        <v>-1743.417016000001</v>
+        <v>-1802.8350412</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2832073371095333</v>
+        <v>0.2957024601152983</v>
       </c>
       <c r="T82">
-        <v>3.672616000503576</v>
+        <v>3.865911579477448</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1083280806343594</v>
+        <v>0.1069906969228241</v>
       </c>
       <c r="W82">
-        <v>0.1790477214086206</v>
+        <v>0.1793162680578969</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4333123225374377</v>
+        <v>0.4279627876912965</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2014296445488032</v>
+        <v>0.2029796445488032</v>
       </c>
       <c r="C83">
-        <v>-15697.23293470589</v>
+        <v>-16217.93311458281</v>
       </c>
       <c r="D83">
-        <v>13823.56906529411</v>
+        <v>13697.41088541719</v>
       </c>
       <c r="E83">
-        <v>23159.102</v>
+        <v>23553.644</v>
       </c>
       <c r="F83">
-        <v>31957.902</v>
+        <v>32352.444</v>
       </c>
       <c r="G83">
         <v>2437.1</v>
@@ -8099,37 +8099,37 @@
         <v>2746.3</v>
       </c>
       <c r="M83">
-        <v>6417.1467216</v>
+        <v>6496.370755200001</v>
       </c>
       <c r="N83">
-        <v>-3670.8467216</v>
+        <v>-3750.0707552</v>
       </c>
       <c r="O83">
-        <v>-917.7116804</v>
+        <v>-937.5176888000001</v>
       </c>
       <c r="P83">
-        <v>-2753.1350412</v>
+        <v>-2812.5530664</v>
       </c>
       <c r="Q83">
-        <v>-1802.8350412</v>
+        <v>-1862.2530664</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2957024601152983</v>
+        <v>0.3095859301217037</v>
       </c>
       <c r="T83">
-        <v>3.865911579477448</v>
+        <v>4.080684445003973</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1069906969228241</v>
+        <v>0.1056859323262043</v>
       </c>
       <c r="W83">
-        <v>0.1793162680578969</v>
+        <v>0.1795782647888982</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4279627876912965</v>
+        <v>0.4227437293048173</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2029796445488032</v>
+        <v>0.2045296445488032</v>
       </c>
       <c r="C84">
-        <v>-16217.93311458281</v>
+        <v>-16736.35140233808</v>
       </c>
       <c r="D84">
-        <v>13697.41088541719</v>
+        <v>13573.53459766192</v>
       </c>
       <c r="E84">
-        <v>23553.644</v>
+        <v>23948.186</v>
       </c>
       <c r="F84">
-        <v>32352.444</v>
+        <v>32746.986</v>
       </c>
       <c r="G84">
         <v>2437.1</v>
@@ -8181,37 +8181,37 @@
         <v>2746.3</v>
       </c>
       <c r="M84">
-        <v>6496.370755200001</v>
+        <v>6575.5947888</v>
       </c>
       <c r="N84">
-        <v>-3750.0707552</v>
+        <v>-3829.2947888</v>
       </c>
       <c r="O84">
-        <v>-937.5176888000001</v>
+        <v>-957.3236972</v>
       </c>
       <c r="P84">
-        <v>-2812.5530664</v>
+        <v>-2871.9710916</v>
       </c>
       <c r="Q84">
-        <v>-1862.2530664</v>
+        <v>-1921.6710916</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3095859301217037</v>
+        <v>0.3251027495406275</v>
       </c>
       <c r="T84">
-        <v>4.080684445003973</v>
+        <v>4.320724706474795</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1056859323262043</v>
+        <v>0.1044126078403464</v>
       </c>
       <c r="W84">
-        <v>0.1795782647888982</v>
+        <v>0.1798339483456584</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4227437293048173</v>
+        <v>0.4176504313613857</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2045296445488032</v>
+        <v>0.2060796445488032</v>
       </c>
       <c r="C85">
-        <v>-16736.35140233808</v>
+        <v>-17252.54915383276</v>
       </c>
       <c r="D85">
-        <v>13573.53459766192</v>
+        <v>13451.87884616723</v>
       </c>
       <c r="E85">
-        <v>23948.186</v>
+        <v>24342.728</v>
       </c>
       <c r="F85">
-        <v>32746.986</v>
+        <v>33141.528</v>
       </c>
       <c r="G85">
         <v>2437.1</v>
@@ -8263,37 +8263,37 @@
         <v>2746.3</v>
       </c>
       <c r="M85">
-        <v>6575.5947888</v>
+        <v>6654.8188224</v>
       </c>
       <c r="N85">
-        <v>-3829.2947888</v>
+        <v>-3908.518822399999</v>
       </c>
       <c r="O85">
-        <v>-957.3236972</v>
+        <v>-977.1297055999999</v>
       </c>
       <c r="P85">
-        <v>-2871.9710916</v>
+        <v>-2931.3891168</v>
       </c>
       <c r="Q85">
-        <v>-1921.6710916</v>
+        <v>-1981.0891168</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3251027495406275</v>
+        <v>0.3425591713869168</v>
       </c>
       <c r="T85">
-        <v>4.320724706474795</v>
+        <v>4.590770000629471</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1044126078403464</v>
+        <v>0.1031696006041518</v>
       </c>
       <c r="W85">
-        <v>0.1798339483456584</v>
+        <v>0.1800835441986863</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4176504313613857</v>
+        <v>0.4126784024166074</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2060796445488032</v>
+        <v>0.2076296445488032</v>
       </c>
       <c r="C86">
-        <v>-17252.54915383276</v>
+        <v>-17766.5855448068</v>
       </c>
       <c r="D86">
-        <v>13451.87884616723</v>
+        <v>13332.38445519319</v>
       </c>
       <c r="E86">
-        <v>24342.728</v>
+        <v>24737.27</v>
       </c>
       <c r="F86">
-        <v>33141.528</v>
+        <v>33536.07</v>
       </c>
       <c r="G86">
         <v>2437.1</v>
@@ -8345,37 +8345,37 @@
         <v>2746.3</v>
       </c>
       <c r="M86">
-        <v>6654.8188224</v>
+        <v>6734.042856</v>
       </c>
       <c r="N86">
-        <v>-3908.518822399999</v>
+        <v>-3987.742856</v>
       </c>
       <c r="O86">
-        <v>-977.1297055999999</v>
+        <v>-996.935714</v>
       </c>
       <c r="P86">
-        <v>-2931.3891168</v>
+        <v>-2990.807142</v>
       </c>
       <c r="Q86">
-        <v>-1981.0891168</v>
+        <v>-2040.507142</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3425591713869166</v>
+        <v>0.3623431161460443</v>
       </c>
       <c r="T86">
-        <v>4.590770000629468</v>
+        <v>4.896821334004765</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1031696006041518</v>
+        <v>0.1019558405970442</v>
       </c>
       <c r="W86">
-        <v>0.1800835441986863</v>
+        <v>0.1803272672081135</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4126784024166074</v>
+        <v>0.4078233623881766</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2076296445488032</v>
+        <v>0.2091796445488032</v>
       </c>
       <c r="C87">
-        <v>-17766.5855448068</v>
+        <v>-18278.5176668576</v>
       </c>
       <c r="D87">
-        <v>13332.38445519319</v>
+        <v>13214.99433314239</v>
       </c>
       <c r="E87">
-        <v>24737.27</v>
+        <v>25131.81199999999</v>
       </c>
       <c r="F87">
-        <v>33536.07</v>
+        <v>33930.61199999999</v>
       </c>
       <c r="G87">
         <v>2437.1</v>
@@ -8427,37 +8427,37 @@
         <v>2746.3</v>
       </c>
       <c r="M87">
-        <v>6734.042856</v>
+        <v>6813.266889599999</v>
       </c>
       <c r="N87">
-        <v>-3987.742856</v>
+        <v>-4066.966889599998</v>
       </c>
       <c r="O87">
-        <v>-996.935714</v>
+        <v>-1016.7417224</v>
       </c>
       <c r="P87">
-        <v>-2990.807142</v>
+        <v>-3050.225167199999</v>
       </c>
       <c r="Q87">
-        <v>-2040.507142</v>
+        <v>-2099.925167199999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3623431161460443</v>
+        <v>0.3849533387279047</v>
       </c>
       <c r="T87">
-        <v>4.896821334004765</v>
+        <v>5.246594286433678</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1019558405970442</v>
+        <v>0.100770307566846</v>
       </c>
       <c r="W87">
-        <v>0.1803272672081135</v>
+        <v>0.1805653222405773</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4078233623881766</v>
+        <v>0.403081230267384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2091796445488032</v>
+        <v>0.2107296445488032</v>
       </c>
       <c r="C88">
-        <v>-18278.5176668576</v>
+        <v>-18788.40061839242</v>
       </c>
       <c r="D88">
-        <v>13214.99433314239</v>
+        <v>13099.65338160757</v>
       </c>
       <c r="E88">
-        <v>25131.81199999999</v>
+        <v>25526.354</v>
       </c>
       <c r="F88">
-        <v>33930.61199999999</v>
+        <v>34325.15399999999</v>
       </c>
       <c r="G88">
         <v>2437.1</v>
@@ -8509,37 +8509,37 @@
         <v>2746.3</v>
       </c>
       <c r="M88">
-        <v>6813.266889599999</v>
+        <v>6892.490923199999</v>
       </c>
       <c r="N88">
-        <v>-4066.966889599998</v>
+        <v>-4146.190923199999</v>
       </c>
       <c r="O88">
-        <v>-1016.7417224</v>
+        <v>-1036.5477308</v>
       </c>
       <c r="P88">
-        <v>-3050.225167199999</v>
+        <v>-3109.643192399999</v>
       </c>
       <c r="Q88">
-        <v>-2099.925167199999</v>
+        <v>-2159.343192399999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3849533387279047</v>
+        <v>0.4110420570915896</v>
       </c>
       <c r="T88">
-        <v>5.246594286433678</v>
+        <v>5.650178462313191</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.100770307566846</v>
+        <v>0.09961202816952593</v>
       </c>
       <c r="W88">
-        <v>0.1805653222405773</v>
+        <v>0.1807979047435592</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.403081230267384</v>
+        <v>0.3984481126781036</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2107296445488032</v>
+        <v>0.2122796445488032</v>
       </c>
       <c r="C89">
-        <v>-18788.40061839242</v>
+        <v>-19296.28759085893</v>
       </c>
       <c r="D89">
-        <v>13099.65338160757</v>
+        <v>12986.30840914106</v>
       </c>
       <c r="E89">
-        <v>25526.354</v>
+        <v>25920.896</v>
       </c>
       <c r="F89">
-        <v>34325.15399999999</v>
+        <v>34719.696</v>
       </c>
       <c r="G89">
         <v>2437.1</v>
@@ -8591,37 +8591,37 @@
         <v>2746.3</v>
       </c>
       <c r="M89">
-        <v>6892.490923199999</v>
+        <v>6971.7149568</v>
       </c>
       <c r="N89">
-        <v>-4146.190923199999</v>
+        <v>-4225.414956799999</v>
       </c>
       <c r="O89">
-        <v>-1036.5477308</v>
+        <v>-1056.3537392</v>
       </c>
       <c r="P89">
-        <v>-3109.643192399999</v>
+        <v>-3169.0612176</v>
       </c>
       <c r="Q89">
-        <v>-2159.343192399999</v>
+        <v>-2218.761217599999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4110420570915896</v>
+        <v>0.4414788951825555</v>
       </c>
       <c r="T89">
-        <v>5.650178462313191</v>
+        <v>6.121026667505959</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09961202816952593</v>
+        <v>0.09848007330396312</v>
       </c>
       <c r="W89">
-        <v>0.1807979047435592</v>
+        <v>0.1810252012805642</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3984481126781036</v>
+        <v>0.3939202932158525</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2122796445488032</v>
+        <v>0.2138296445488032</v>
       </c>
       <c r="C90">
-        <v>-19296.28759085893</v>
+        <v>-19802.22995053746</v>
       </c>
       <c r="D90">
-        <v>12986.30840914106</v>
+        <v>12874.90804946253</v>
       </c>
       <c r="E90">
-        <v>25920.896</v>
+        <v>26315.438</v>
       </c>
       <c r="F90">
-        <v>34719.696</v>
+        <v>35114.238</v>
       </c>
       <c r="G90">
         <v>2437.1</v>
@@ -8673,37 +8673,37 @@
         <v>2746.3</v>
       </c>
       <c r="M90">
-        <v>6971.7149568</v>
+        <v>7050.9389904</v>
       </c>
       <c r="N90">
-        <v>-4225.414956799999</v>
+        <v>-4304.6389904</v>
       </c>
       <c r="O90">
-        <v>-1056.3537392</v>
+        <v>-1076.1597476</v>
       </c>
       <c r="P90">
-        <v>-3169.0612176</v>
+        <v>-3228.4792428</v>
       </c>
       <c r="Q90">
-        <v>-2218.761217599999</v>
+        <v>-2278.1792428</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4414788951825555</v>
+        <v>0.4774497038355152</v>
       </c>
       <c r="T90">
-        <v>6.121026667505959</v>
+        <v>6.677483637279228</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09848007330396312</v>
+        <v>0.0973735556263905</v>
       </c>
       <c r="W90">
-        <v>0.1810252012805642</v>
+        <v>0.1812473900302208</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3939202932158525</v>
+        <v>0.389494222505562</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2138296445488032</v>
+        <v>0.2153796445488032</v>
       </c>
       <c r="C91">
-        <v>-19802.22995053746</v>
+        <v>-20306.27731615931</v>
       </c>
       <c r="D91">
-        <v>12874.90804946253</v>
+        <v>12765.40268384069</v>
       </c>
       <c r="E91">
-        <v>26315.438</v>
+        <v>26709.98</v>
       </c>
       <c r="F91">
-        <v>35114.238</v>
+        <v>35508.78</v>
       </c>
       <c r="G91">
         <v>2437.1</v>
@@ -8755,37 +8755,37 @@
         <v>2746.3</v>
       </c>
       <c r="M91">
-        <v>7050.9389904</v>
+        <v>7130.163024</v>
       </c>
       <c r="N91">
-        <v>-4304.6389904</v>
+        <v>-4383.863024</v>
       </c>
       <c r="O91">
-        <v>-1076.1597476</v>
+        <v>-1095.965756</v>
       </c>
       <c r="P91">
-        <v>-3228.4792428</v>
+        <v>-3287.897268</v>
       </c>
       <c r="Q91">
-        <v>-2278.1792428</v>
+        <v>-2337.597268</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4774497038355152</v>
+        <v>0.5206146742190666</v>
       </c>
       <c r="T91">
-        <v>6.677483637279228</v>
+        <v>7.345232001007151</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.0973735556263905</v>
+        <v>0.0962916272305417</v>
       </c>
       <c r="W91">
-        <v>0.1812473900302208</v>
+        <v>0.1814646412521072</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.389494222505562</v>
+        <v>0.3851665089221669</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2153796445488032</v>
+        <v>0.2169296445488031</v>
       </c>
       <c r="C92">
-        <v>-20306.27731615931</v>
+        <v>-20808.4776325974</v>
       </c>
       <c r="D92">
-        <v>12765.40268384069</v>
+        <v>12657.7443674026</v>
       </c>
       <c r="E92">
-        <v>26709.98</v>
+        <v>27104.522</v>
       </c>
       <c r="F92">
-        <v>35508.78</v>
+        <v>35903.322</v>
       </c>
       <c r="G92">
         <v>2437.1</v>
@@ -8837,37 +8837,37 @@
         <v>2746.3</v>
       </c>
       <c r="M92">
-        <v>7130.163024</v>
+        <v>7209.3870576</v>
       </c>
       <c r="N92">
-        <v>-4383.863024</v>
+        <v>-4463.0870576</v>
       </c>
       <c r="O92">
-        <v>-1095.965756</v>
+        <v>-1115.7717644</v>
       </c>
       <c r="P92">
-        <v>-3287.897268</v>
+        <v>-3347.3152932</v>
       </c>
       <c r="Q92">
-        <v>-2337.597268</v>
+        <v>-2397.0152932</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5206146742190666</v>
+        <v>0.5733718602434074</v>
       </c>
       <c r="T92">
-        <v>7.345232001007151</v>
+        <v>8.161368890007946</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.0962916272305417</v>
+        <v>0.09523347748075554</v>
       </c>
       <c r="W92">
-        <v>0.1814646412521072</v>
+        <v>0.1816771177218643</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3851665089221669</v>
+        <v>0.3809339099230221</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2169296445488031</v>
+        <v>0.2184796445488031</v>
       </c>
       <c r="C93">
-        <v>-20808.4776325974</v>
+        <v>-21308.87724085924</v>
       </c>
       <c r="D93">
-        <v>12657.7443674026</v>
+        <v>12551.88675914076</v>
       </c>
       <c r="E93">
-        <v>27104.522</v>
+        <v>27499.064</v>
       </c>
       <c r="F93">
-        <v>35903.322</v>
+        <v>36297.864</v>
       </c>
       <c r="G93">
         <v>2437.1</v>
@@ -8919,37 +8919,37 @@
         <v>2746.3</v>
       </c>
       <c r="M93">
-        <v>7209.3870576</v>
+        <v>7288.6110912</v>
       </c>
       <c r="N93">
-        <v>-4463.0870576</v>
+        <v>-4542.3110912</v>
       </c>
       <c r="O93">
-        <v>-1115.7717644</v>
+        <v>-1135.5777728</v>
       </c>
       <c r="P93">
-        <v>-3347.3152932</v>
+        <v>-3406.7333184</v>
       </c>
       <c r="Q93">
-        <v>-2397.0152932</v>
+        <v>-2456.4333184</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5733718602434074</v>
+        <v>0.6393183427738335</v>
       </c>
       <c r="T93">
-        <v>8.161368890007946</v>
+        <v>9.181540001258941</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09523347748075554</v>
+        <v>0.0941983309863995</v>
       </c>
       <c r="W93">
-        <v>0.1816771177218643</v>
+        <v>0.181884975137931</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3809339099230221</v>
+        <v>0.3767933239455979</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2184796445488031</v>
+        <v>0.2200296445488031</v>
       </c>
       <c r="C94">
-        <v>-21308.87724085924</v>
+        <v>-21807.5209445969</v>
       </c>
       <c r="D94">
-        <v>12551.88675914076</v>
+        <v>12447.7850554031</v>
       </c>
       <c r="E94">
-        <v>27499.064</v>
+        <v>27893.606</v>
       </c>
       <c r="F94">
-        <v>36297.864</v>
+        <v>36692.406</v>
       </c>
       <c r="G94">
         <v>2437.1</v>
@@ -9001,37 +9001,37 @@
         <v>2746.3</v>
       </c>
       <c r="M94">
-        <v>7288.6110912</v>
+        <v>7367.835124800001</v>
       </c>
       <c r="N94">
-        <v>-4542.3110912</v>
+        <v>-4621.535124800001</v>
       </c>
       <c r="O94">
-        <v>-1135.5777728</v>
+        <v>-1155.3837812</v>
       </c>
       <c r="P94">
-        <v>-3406.7333184</v>
+        <v>-3466.1513436</v>
       </c>
       <c r="Q94">
-        <v>-2456.4333184</v>
+        <v>-2515.8513436</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6393183427738335</v>
+        <v>0.7241066774558098</v>
       </c>
       <c r="T94">
-        <v>9.181540001258941</v>
+        <v>10.49318857286736</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.0941983309863995</v>
+        <v>0.09318544570697584</v>
       </c>
       <c r="W94">
-        <v>0.181884975137931</v>
+        <v>0.1820883625020392</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3767933239455979</v>
+        <v>0.3727417828279034</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2200296445488031</v>
+        <v>0.2215796445488032</v>
       </c>
       <c r="C95">
-        <v>-21807.5209445969</v>
+        <v>-22304.45207333454</v>
       </c>
       <c r="D95">
-        <v>12447.7850554031</v>
+        <v>12345.39592666546</v>
       </c>
       <c r="E95">
-        <v>27893.606</v>
+        <v>28288.148</v>
       </c>
       <c r="F95">
-        <v>36692.406</v>
+        <v>37086.948</v>
       </c>
       <c r="G95">
         <v>2437.1</v>
@@ -9083,37 +9083,37 @@
         <v>2746.3</v>
       </c>
       <c r="M95">
-        <v>7367.835124800001</v>
+        <v>7447.059158399999</v>
       </c>
       <c r="N95">
-        <v>-4621.535124800001</v>
+        <v>-4700.759158399999</v>
       </c>
       <c r="O95">
-        <v>-1155.3837812</v>
+        <v>-1175.1897896</v>
       </c>
       <c r="P95">
-        <v>-3466.1513436</v>
+        <v>-3525.569368799999</v>
       </c>
       <c r="Q95">
-        <v>-2515.8513436</v>
+        <v>-2575.269368799999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7241066774558098</v>
+        <v>0.8371577903651115</v>
       </c>
       <c r="T95">
-        <v>10.49318857286736</v>
+        <v>12.24205333501193</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09318544570697584</v>
+        <v>0.09219411117817825</v>
       </c>
       <c r="W95">
-        <v>0.1820883625020392</v>
+        <v>0.1822874224754218</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3727417828279034</v>
+        <v>0.368776444712713</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2215796445488032</v>
+        <v>0.2231296445488032</v>
       </c>
       <c r="C96">
-        <v>-22304.45207333454</v>
+        <v>-22799.71254260087</v>
       </c>
       <c r="D96">
-        <v>12345.39592666546</v>
+        <v>12244.67745739913</v>
       </c>
       <c r="E96">
-        <v>28288.148</v>
+        <v>28682.69</v>
       </c>
       <c r="F96">
-        <v>37086.948</v>
+        <v>37481.49</v>
       </c>
       <c r="G96">
         <v>2437.1</v>
@@ -9165,37 +9165,37 @@
         <v>2746.3</v>
       </c>
       <c r="M96">
-        <v>7447.059158399999</v>
+        <v>7526.283192</v>
       </c>
       <c r="N96">
-        <v>-4700.759158399999</v>
+        <v>-4779.983192</v>
       </c>
       <c r="O96">
-        <v>-1175.1897896</v>
+        <v>-1194.995798</v>
       </c>
       <c r="P96">
-        <v>-3525.569368799999</v>
+        <v>-3584.987394</v>
       </c>
       <c r="Q96">
-        <v>-2575.269368799999</v>
+        <v>-2634.687394</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8371577903651115</v>
+        <v>0.9954293484381345</v>
       </c>
       <c r="T96">
-        <v>12.24205333501193</v>
+        <v>14.69046400201432</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09219411117817825</v>
+        <v>0.09122364684998689</v>
       </c>
       <c r="W96">
-        <v>0.1822874224754218</v>
+        <v>0.1824822917125226</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.368776444712713</v>
+        <v>0.3648945873999475</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2231296445488032</v>
+        <v>0.2246796445488032</v>
       </c>
       <c r="C97">
-        <v>-22799.71254260087</v>
+        <v>-23293.342911142</v>
       </c>
       <c r="D97">
-        <v>12244.67745739913</v>
+        <v>12145.589088858</v>
       </c>
       <c r="E97">
-        <v>28682.69</v>
+        <v>29077.232</v>
       </c>
       <c r="F97">
-        <v>37481.49</v>
+        <v>37876.032</v>
       </c>
       <c r="G97">
         <v>2437.1</v>
@@ -9247,37 +9247,37 @@
         <v>2746.3</v>
       </c>
       <c r="M97">
-        <v>7526.283192</v>
+        <v>7605.5072256</v>
       </c>
       <c r="N97">
-        <v>-4779.983192</v>
+        <v>-4859.2072256</v>
       </c>
       <c r="O97">
-        <v>-1194.995798</v>
+        <v>-1214.8018064</v>
       </c>
       <c r="P97">
-        <v>-3584.987394</v>
+        <v>-3644.4054192</v>
       </c>
       <c r="Q97">
-        <v>-2634.687394</v>
+        <v>-2694.1054192</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9954293484381345</v>
+        <v>1.232836685547669</v>
       </c>
       <c r="T97">
-        <v>14.69046400201432</v>
+        <v>18.36308000251791</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09122364684998689</v>
+        <v>0.09027340052863285</v>
       </c>
       <c r="W97">
-        <v>0.1824822917125226</v>
+        <v>0.1826731011738505</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3648945873999475</v>
+        <v>0.3610936021145315</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2246796445488032</v>
+        <v>0.2262296445488031</v>
       </c>
       <c r="C98">
-        <v>-23293.342911142</v>
+        <v>-23785.38243537862</v>
       </c>
       <c r="D98">
-        <v>12145.589088858</v>
+        <v>12048.09156462137</v>
       </c>
       <c r="E98">
-        <v>29077.232</v>
+        <v>29471.77399999999</v>
       </c>
       <c r="F98">
-        <v>37876.032</v>
+        <v>38270.57399999999</v>
       </c>
       <c r="G98">
         <v>2437.1</v>
@@ -9329,37 +9329,37 @@
         <v>2746.3</v>
       </c>
       <c r="M98">
-        <v>7605.5072256</v>
+        <v>7684.731259199999</v>
       </c>
       <c r="N98">
-        <v>-4859.2072256</v>
+        <v>-4938.431259199999</v>
       </c>
       <c r="O98">
-        <v>-1214.8018064</v>
+        <v>-1234.6078148</v>
       </c>
       <c r="P98">
-        <v>-3644.4054192</v>
+        <v>-3703.823444399999</v>
       </c>
       <c r="Q98">
-        <v>-2694.1054192</v>
+        <v>-2753.523444399999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.232836685547666</v>
+        <v>1.628515580730221</v>
       </c>
       <c r="T98">
-        <v>18.36308000251786</v>
+        <v>24.48410667002381</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09027340052863285</v>
+        <v>0.08934274691493563</v>
       </c>
       <c r="W98">
-        <v>0.1826731011738505</v>
+        <v>0.1828599764194809</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3610936021145315</v>
+        <v>0.3573709876597425</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2262296445488031</v>
+        <v>0.2277796445488032</v>
       </c>
       <c r="C99">
-        <v>-23785.38243537862</v>
+        <v>-24275.86912126122</v>
       </c>
       <c r="D99">
-        <v>12048.09156462137</v>
+        <v>11952.14687873877</v>
       </c>
       <c r="E99">
-        <v>29471.77399999999</v>
+        <v>29866.316</v>
       </c>
       <c r="F99">
-        <v>38270.57399999999</v>
+        <v>38665.11599999999</v>
       </c>
       <c r="G99">
         <v>2437.1</v>
@@ -9411,37 +9411,37 @@
         <v>2746.3</v>
       </c>
       <c r="M99">
-        <v>7684.731259199999</v>
+        <v>7763.955292799999</v>
       </c>
       <c r="N99">
-        <v>-4938.431259199999</v>
+        <v>-5017.655292799999</v>
       </c>
       <c r="O99">
-        <v>-1234.6078148</v>
+        <v>-1254.4138232</v>
       </c>
       <c r="P99">
-        <v>-3703.823444399999</v>
+        <v>-3763.2414696</v>
       </c>
       <c r="Q99">
-        <v>-2753.523444399999</v>
+        <v>-2812.941469599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.628515580730221</v>
+        <v>2.419873371095331</v>
       </c>
       <c r="T99">
-        <v>24.48410667002381</v>
+        <v>36.72616000503572</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08934274691493563</v>
+        <v>0.08843108623213015</v>
       </c>
       <c r="W99">
-        <v>0.1828599764194809</v>
+        <v>0.1830430378845883</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3573709876597425</v>
+        <v>0.3537243449285206</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2277796445488032</v>
+        <v>0.2293296445488032</v>
       </c>
       <c r="C100">
-        <v>-24275.86912126122</v>
+        <v>-24764.8397736671</v>
       </c>
       <c r="D100">
-        <v>11952.14687873877</v>
+        <v>11857.71822633289</v>
       </c>
       <c r="E100">
-        <v>29866.316</v>
+        <v>30260.858</v>
       </c>
       <c r="F100">
-        <v>38665.11599999999</v>
+        <v>39059.658</v>
       </c>
       <c r="G100">
         <v>2437.1</v>
@@ -9493,37 +9493,37 @@
         <v>2746.3</v>
       </c>
       <c r="M100">
-        <v>7763.955292799999</v>
+        <v>7843.1793264</v>
       </c>
       <c r="N100">
-        <v>-5017.655292799999</v>
+        <v>-5096.8793264</v>
       </c>
       <c r="O100">
-        <v>-1254.4138232</v>
+        <v>-1274.2198316</v>
       </c>
       <c r="P100">
-        <v>-3763.2414696</v>
+        <v>-3822.6594948</v>
       </c>
       <c r="Q100">
-        <v>-2812.941469599999</v>
+        <v>-2872.3594948</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.419873371095331</v>
+        <v>4.793946742190662</v>
       </c>
       <c r="T100">
-        <v>36.72616000503572</v>
+        <v>73.45232001007143</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08843108623213015</v>
+        <v>0.08753784293685611</v>
       </c>
       <c r="W100">
-        <v>0.1830430378845883</v>
+        <v>0.1832224011382793</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3537243449285206</v>
+        <v>0.3501513717474244</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2293296445488032</v>
-      </c>
-      <c r="C101">
-        <v>-24764.8397736671</v>
-      </c>
-      <c r="D101">
-        <v>11857.71822633289</v>
-      </c>
-      <c r="E101">
-        <v>30260.858</v>
-      </c>
-      <c r="F101">
-        <v>39059.658</v>
-      </c>
-      <c r="G101">
-        <v>2437.1</v>
-      </c>
-      <c r="H101">
-        <v>30655.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3696.6</v>
-      </c>
-      <c r="K101">
-        <v>950.3</v>
-      </c>
-      <c r="L101">
-        <v>2746.3</v>
-      </c>
-      <c r="M101">
-        <v>7843.1793264</v>
-      </c>
-      <c r="N101">
-        <v>-5096.8793264</v>
-      </c>
-      <c r="O101">
-        <v>-1274.2198316</v>
-      </c>
-      <c r="P101">
-        <v>-3822.6594948</v>
-      </c>
-      <c r="Q101">
-        <v>-2872.3594948</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.793946742190662</v>
-      </c>
-      <c r="T101">
-        <v>73.45232001007143</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.08753784293685611</v>
-      </c>
-      <c r="W101">
-        <v>0.1832224011382793</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3501513717474244</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
